--- a/جدول_الورديات_وحجز_الإجازات.xlsx
+++ b/جدول_الورديات_وحجز_الإجازات.xlsx
@@ -97,7 +97,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -141,17 +141,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008EAADB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="008EA9DB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -186,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -201,6 +211,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -213,10 +226,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -226,9 +251,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,29 +268,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -293,7 +330,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="008EAADB"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="1"/>
@@ -365,13 +423,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -744,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B29"/>
+  <dimension ref="B1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -823,112 +874,126 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>• بداية الدوام اليومي: 2:00 عصراً.</t>
+          <t>• ثلاث ورديات (زامات):</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>• الجدول يحسب الحالة (عمل/راحة) آلياً حسب «بداية الدورة» في ورقة الموظفين.</t>
+          <t xml:space="preserve">     صباح: 6:00 ص ← 1:00 م   |   عصر: 1:00 م ← 9:00 م   |   ليل: 9:00 م ← 6:00 ص (اليوم التالي).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>• وردية كل موظف تُحدَّد من عمود «الوردية» في ورقة الموظفين (قابلة للتغيير).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>• الجدول يعرض اسم وردية الموظف على أيام عمله و«راحة» على أيام راحته — تلقائياً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>أنواع الإجازات:</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>سنوية • عارض • دورية • مرضية • مرافق مريض • أخرى</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>كيف أحجز إجازة بدون تعارض؟</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>1) افتح ورقة «حجز الإجازات».</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>2) اختر اسم الموظف ونوع الإجازة من القائمة المنسدلة، وأدخل تاريخ البداية والنهاية.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>3) عمود «عدد الأيام» يُحسب تلقائياً، وعمود «فحص التعارض» يتحقق فوراً:</t>
+          <t>1) افتح ورقة «حجز الإجازات».</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     ✓ سليم = لا يوجد تعارض   |   ⚠ تعارض = للموظف إجازة أخرى متداخلة بنفس الفترة.</t>
+          <t>2) اختر اسم الموظف ونوع الإجازة من القائمة المنسدلة، وأدخل تاريخ البداية والنهاية.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>4) عمود «تنبيه التغطية» ينبّه إذا تجاوز عدد المُجازين في نفس اليوم الحد المسموح.</t>
+          <t>3) عمود «عدد الأيام» يُحسب تلقائياً، وعمود «فحص التعارض» يتحقق فوراً:</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">     ✓ سليم = لا يوجد تعارض   |   ⚠ تعارض = للموظف إجازة أخرى متداخلة بنفس الفترة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>4) عمود «تنبيه التغطية» ينبّه إذا تجاوز عدد المُجازين في نفس اليوم الحد المسموح.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>5) غيّر «الحالة» إلى «معتمد» لتظهر الإجازة ملوّنة في جدول الورديات.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>ملاحظات:</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>• الصفوف الحمراء/التنبيهات تعني وجود تعارض — عالجه قبل الاعتماد.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>• في «جدول الورديات» يظهر أسفل كل يوم: عدد العاملين وعدد المُجازين؛ ويتلوّن بالأحمر عند نقص التغطية.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>• الصفوف الحمراء/التنبيهات تعني وجود تعارض — عالجه قبل الاعتماد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>• في «جدول الورديات» يظهر أسفل كل يوم: عدد العاملين وعدد المُجازين؛ ويتلوّن بالأحمر عند نقص التغطية.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>• كل التواريخ بصيغة يوم/شهر/سنة. عدّل «بداية الفترة» وعدد الموظفين بحرية.</t>
         </is>
@@ -945,13 +1010,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,99 +1037,139 @@
           <t>حالات الطلب</t>
         </is>
       </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>الوردية</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>التوقيت</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>بداية فترة الجدول</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="8" t="n">
         <v>46189</v>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>سنوية</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>معتمد</t>
         </is>
       </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>صباح</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>6:00 ص ← 1:00 م</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>طول دورة العمل (أيام)</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>عارض</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>قيد الانتظار</t>
         </is>
       </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>1:00 م ← 9:00 م</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>طول الراحة الدورية (أيام)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>دورية</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>مرفوض</t>
         </is>
       </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>ليل</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>9:00 م ← 6:00 ص (اليوم التالي)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>الحد الأدنى للعاملين يومياً</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>مرضية</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>أقصى عدد مُجازين في اليوم</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>مرافق مريض</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>أخرى</t>
         </is>
@@ -1079,166 +1186,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>الرقم الوظيفي</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>الوردية</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>بداية الدورة</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>سالم شليويح المري</t>
         </is>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="20" t="n">
         <v>392</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>فهد عبدالعزيز عبدالله</t>
         </is>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="20" t="n">
         <v>2306</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>محمد ناصر الغانم</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="20" t="n">
         <v>4756</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>راشد عيسى التميمي</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="20" t="n">
         <v>4749</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>طلال زايد المري</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="20" t="n">
         <v>2927</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>منصور مبارك الجابري</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="20" t="n">
         <v>4522</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>محمد حمد الجابر</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="20" t="n">
         <v>3317</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>عبدالله سعد المهندي</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="20" t="n">
         <v>2424</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
         <v>46189</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"صباح"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"عصر"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"ليل"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='الإعدادات والقوائم'!$H$2:$H$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1265,2402 +1434,2402 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>حجز الإجازات — قسم العمليات الجمركية</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>سجّل الطلب ثم تأكد من خانتي «فحص التعارض» و«تنبيه التغطية» قبل الاعتماد.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>رقم الطلب</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>اسم الموظف</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>نوع الإجازة</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>من تاريخ</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>إلى تاريخ</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>عدد الأيام</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>فحص التعارض</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>تنبيه التغطية</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="16">
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="20">
         <f>IF(OR($D5="",$E5=""),"",$E5-$D5+1)</f>
         <v/>
       </c>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16">
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20">
         <f>IF(OR($B5="",$D5="",$E5=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B5)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B5&lt;&gt;"")*($G5&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="20">
         <f>IF($D5="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J5" s="17" t="n"/>
+      <c r="J5" s="21" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
-      <c r="F6" s="16">
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="20">
         <f>IF(OR($D6="",$E6=""),"",$E6-$D6+1)</f>
         <v/>
       </c>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16">
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20">
         <f>IF(OR($B6="",$D6="",$E6=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B6)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B6&lt;&gt;"")*($G6&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="20">
         <f>IF($D6="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J6" s="17" t="n"/>
+      <c r="J6" s="21" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="16">
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="25" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="20">
         <f>IF(OR($D7="",$E7=""),"",$E7-$D7+1)</f>
         <v/>
       </c>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16">
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20">
         <f>IF(OR($B7="",$D7="",$E7=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B7)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B7&lt;&gt;"")*($G7&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="20">
         <f>IF($D7="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J7" s="17" t="n"/>
+      <c r="J7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="16">
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="20">
         <f>IF(OR($D8="",$E8=""),"",$E8-$D8+1)</f>
         <v/>
       </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16">
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20">
         <f>IF(OR($B8="",$D8="",$E8=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B8)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B8&lt;&gt;"")*($G8&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="20">
         <f>IF($D8="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J8" s="17" t="n"/>
+      <c r="J8" s="21" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="16">
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="25" t="n"/>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="20">
         <f>IF(OR($D9="",$E9=""),"",$E9-$D9+1)</f>
         <v/>
       </c>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16">
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20">
         <f>IF(OR($B9="",$D9="",$E9=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B9)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B9&lt;&gt;"")*($G9&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="20">
         <f>IF($D9="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J9" s="17" t="n"/>
+      <c r="J9" s="21" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="16">
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="20">
         <f>IF(OR($D10="",$E10=""),"",$E10-$D10+1)</f>
         <v/>
       </c>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16">
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20">
         <f>IF(OR($B10="",$D10="",$E10=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B10)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B10&lt;&gt;"")*($G10&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="20">
         <f>IF($D10="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J10" s="17" t="n"/>
+      <c r="J10" s="21" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="16">
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="20">
         <f>IF(OR($D11="",$E11=""),"",$E11-$D11+1)</f>
         <v/>
       </c>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16">
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20">
         <f>IF(OR($B11="",$D11="",$E11=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B11)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B11&lt;&gt;"")*($G11&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="20">
         <f>IF($D11="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J11" s="17" t="n"/>
+      <c r="J11" s="21" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="16">
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="20">
         <f>IF(OR($D12="",$E12=""),"",$E12-$D12+1)</f>
         <v/>
       </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16">
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20">
         <f>IF(OR($B12="",$D12="",$E12=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B12)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B12&lt;&gt;"")*($G12&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="20">
         <f>IF($D12="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J12" s="17" t="n"/>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="16">
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="20">
         <f>IF(OR($D13="",$E13=""),"",$E13-$D13+1)</f>
         <v/>
       </c>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16">
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20">
         <f>IF(OR($B13="",$D13="",$E13=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B13)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B13&lt;&gt;"")*($G13&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="20">
         <f>IF($D13="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J13" s="17" t="n"/>
+      <c r="J13" s="21" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="16">
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="20">
         <f>IF(OR($D14="",$E14=""),"",$E14-$D14+1)</f>
         <v/>
       </c>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16">
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20">
         <f>IF(OR($B14="",$D14="",$E14=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B14)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B14&lt;&gt;"")*($G14&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="20">
         <f>IF($D14="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J14" s="17" t="n"/>
+      <c r="J14" s="21" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="16">
+      <c r="B15" s="21" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="20">
         <f>IF(OR($D15="",$E15=""),"",$E15-$D15+1)</f>
         <v/>
       </c>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16">
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20">
         <f>IF(OR($B15="",$D15="",$E15=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B15)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B15&lt;&gt;"")*($G15&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="20">
         <f>IF($D15="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J15" s="17" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="16">
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="20">
         <f>IF(OR($D16="",$E16=""),"",$E16-$D16+1)</f>
         <v/>
       </c>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16">
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20">
         <f>IF(OR($B16="",$D16="",$E16=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B16)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B16&lt;&gt;"")*($G16&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="20">
         <f>IF($D16="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J16" s="17" t="n"/>
+      <c r="J16" s="21" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="16">
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="20">
         <f>IF(OR($D17="",$E17=""),"",$E17-$D17+1)</f>
         <v/>
       </c>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16">
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20">
         <f>IF(OR($B17="",$D17="",$E17=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B17)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B17&lt;&gt;"")*($G17&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="20">
         <f>IF($D17="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J17" s="17" t="n"/>
+      <c r="J17" s="21" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="16">
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="20">
         <f>IF(OR($D18="",$E18=""),"",$E18-$D18+1)</f>
         <v/>
       </c>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16">
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20">
         <f>IF(OR($B18="",$D18="",$E18=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B18)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B18&lt;&gt;"")*($G18&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="20">
         <f>IF($D18="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J18" s="17" t="n"/>
+      <c r="J18" s="21" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="16">
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="20">
         <f>IF(OR($D19="",$E19=""),"",$E19-$D19+1)</f>
         <v/>
       </c>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="16">
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20">
         <f>IF(OR($B19="",$D19="",$E19=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B19)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B19&lt;&gt;"")*($G19&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="20">
         <f>IF($D19="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J19" s="17" t="n"/>
+      <c r="J19" s="21" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="16">
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="20">
         <f>IF(OR($D20="",$E20=""),"",$E20-$D20+1)</f>
         <v/>
       </c>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16">
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20">
         <f>IF(OR($B20="",$D20="",$E20=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B20)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B20&lt;&gt;"")*($G20&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="20">
         <f>IF($D20="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J20" s="17" t="n"/>
+      <c r="J20" s="21" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="16">
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="20">
         <f>IF(OR($D21="",$E21=""),"",$E21-$D21+1)</f>
         <v/>
       </c>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16">
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20">
         <f>IF(OR($B21="",$D21="",$E21=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B21)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B21&lt;&gt;"")*($G21&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="20">
         <f>IF($D21="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J21" s="17" t="n"/>
+      <c r="J21" s="21" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="16">
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="20">
         <f>IF(OR($D22="",$E22=""),"",$E22-$D22+1)</f>
         <v/>
       </c>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16">
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20">
         <f>IF(OR($B22="",$D22="",$E22=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B22)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B22&lt;&gt;"")*($G22&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="20">
         <f>IF($D22="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J22" s="17" t="n"/>
+      <c r="J22" s="21" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="16">
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="20">
         <f>IF(OR($D23="",$E23=""),"",$E23-$D23+1)</f>
         <v/>
       </c>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16">
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20">
         <f>IF(OR($B23="",$D23="",$E23=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B23)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B23&lt;&gt;"")*($G23&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="20">
         <f>IF($D23="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J23" s="17" t="n"/>
+      <c r="J23" s="21" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="16">
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="20">
         <f>IF(OR($D24="",$E24=""),"",$E24-$D24+1)</f>
         <v/>
       </c>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16">
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20">
         <f>IF(OR($B24="",$D24="",$E24=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B24)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B24&lt;&gt;"")*($G24&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="20">
         <f>IF($D24="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J24" s="17" t="n"/>
+      <c r="J24" s="21" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="16">
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="20">
         <f>IF(OR($D25="",$E25=""),"",$E25-$D25+1)</f>
         <v/>
       </c>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16">
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20">
         <f>IF(OR($B25="",$D25="",$E25=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B25)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B25&lt;&gt;"")*($G25&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="20">
         <f>IF($D25="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J25" s="17" t="n"/>
+      <c r="J25" s="21" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="16">
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="20">
         <f>IF(OR($D26="",$E26=""),"",$E26-$D26+1)</f>
         <v/>
       </c>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="16">
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="20">
         <f>IF(OR($B26="",$D26="",$E26=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B26)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B26&lt;&gt;"")*($G26&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="20">
         <f>IF($D26="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J26" s="17" t="n"/>
+      <c r="J26" s="21" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="16">
+      <c r="B27" s="21" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="20">
         <f>IF(OR($D27="",$E27=""),"",$E27-$D27+1)</f>
         <v/>
       </c>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16">
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20">
         <f>IF(OR($B27="",$D27="",$E27=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B27)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B27&lt;&gt;"")*($G27&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="20">
         <f>IF($D27="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J27" s="17" t="n"/>
+      <c r="J27" s="21" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="16">
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="20">
         <f>IF(OR($D28="",$E28=""),"",$E28-$D28+1)</f>
         <v/>
       </c>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="16">
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20">
         <f>IF(OR($B28="",$D28="",$E28=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B28)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B28&lt;&gt;"")*($G28&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="20">
         <f>IF($D28="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J28" s="17" t="n"/>
+      <c r="J28" s="21" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="21" t="n"/>
-      <c r="F29" s="16">
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="20">
         <f>IF(OR($D29="",$E29=""),"",$E29-$D29+1)</f>
         <v/>
       </c>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16">
+      <c r="G29" s="20" t="n"/>
+      <c r="H29" s="20">
         <f>IF(OR($B29="",$D29="",$E29=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B29)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B29&lt;&gt;"")*($G29&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="20">
         <f>IF($D29="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J29" s="17" t="n"/>
+      <c r="J29" s="21" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="16">
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="20">
         <f>IF(OR($D30="",$E30=""),"",$E30-$D30+1)</f>
         <v/>
       </c>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16">
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20">
         <f>IF(OR($B30="",$D30="",$E30=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B30)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B30&lt;&gt;"")*($G30&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="20">
         <f>IF($D30="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J30" s="17" t="n"/>
+      <c r="J30" s="21" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="16">
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="20">
         <f>IF(OR($D31="",$E31=""),"",$E31-$D31+1)</f>
         <v/>
       </c>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16">
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20">
         <f>IF(OR($B31="",$D31="",$E31=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B31)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B31&lt;&gt;"")*($G31&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="20">
         <f>IF($D31="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J31" s="17" t="n"/>
+      <c r="J31" s="21" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="16">
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="20">
         <f>IF(OR($D32="",$E32=""),"",$E32-$D32+1)</f>
         <v/>
       </c>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="16">
+      <c r="G32" s="20" t="n"/>
+      <c r="H32" s="20">
         <f>IF(OR($B32="",$D32="",$E32=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B32)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B32&lt;&gt;"")*($G32&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="20">
         <f>IF($D32="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J32" s="17" t="n"/>
+      <c r="J32" s="21" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="16">
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="25" t="n"/>
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="20">
         <f>IF(OR($D33="",$E33=""),"",$E33-$D33+1)</f>
         <v/>
       </c>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="16">
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="20">
         <f>IF(OR($B33="",$D33="",$E33=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B33)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B33&lt;&gt;"")*($G33&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="20">
         <f>IF($D33="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J33" s="17" t="n"/>
+      <c r="J33" s="21" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="16">
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="20">
         <f>IF(OR($D34="",$E34=""),"",$E34-$D34+1)</f>
         <v/>
       </c>
-      <c r="G34" s="16" t="n"/>
-      <c r="H34" s="16">
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20">
         <f>IF(OR($B34="",$D34="",$E34=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B34)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B34&lt;&gt;"")*($G34&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="20">
         <f>IF($D34="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J34" s="17" t="n"/>
+      <c r="J34" s="21" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="20" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="F35" s="16">
+      <c r="B35" s="21" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="20">
         <f>IF(OR($D35="",$E35=""),"",$E35-$D35+1)</f>
         <v/>
       </c>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="16">
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20">
         <f>IF(OR($B35="",$D35="",$E35=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B35)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B35&lt;&gt;"")*($G35&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="20">
         <f>IF($D35="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J35" s="17" t="n"/>
+      <c r="J35" s="21" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="16">
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="20">
         <f>IF(OR($D36="",$E36=""),"",$E36-$D36+1)</f>
         <v/>
       </c>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="16">
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20">
         <f>IF(OR($B36="",$D36="",$E36=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B36)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B36&lt;&gt;"")*($G36&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="20">
         <f>IF($D36="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J36" s="17" t="n"/>
+      <c r="J36" s="21" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="21" t="n"/>
-      <c r="F37" s="16">
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="20">
         <f>IF(OR($D37="",$E37=""),"",$E37-$D37+1)</f>
         <v/>
       </c>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16">
+      <c r="G37" s="20" t="n"/>
+      <c r="H37" s="20">
         <f>IF(OR($B37="",$D37="",$E37=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B37)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B37&lt;&gt;"")*($G37&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="20">
         <f>IF($D37="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J37" s="17" t="n"/>
+      <c r="J37" s="21" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="17" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="16">
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="25" t="n"/>
+      <c r="E38" s="25" t="n"/>
+      <c r="F38" s="20">
         <f>IF(OR($D38="",$E38=""),"",$E38-$D38+1)</f>
         <v/>
       </c>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="16">
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20">
         <f>IF(OR($B38="",$D38="",$E38=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B38)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B38&lt;&gt;"")*($G38&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="20">
         <f>IF($D38="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J38" s="17" t="n"/>
+      <c r="J38" s="21" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n">
+      <c r="A39" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="16">
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="25" t="n"/>
+      <c r="E39" s="25" t="n"/>
+      <c r="F39" s="20">
         <f>IF(OR($D39="",$E39=""),"",$E39-$D39+1)</f>
         <v/>
       </c>
-      <c r="G39" s="16" t="n"/>
-      <c r="H39" s="16">
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20">
         <f>IF(OR($B39="",$D39="",$E39=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B39)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B39&lt;&gt;"")*($G39&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="20">
         <f>IF($D39="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J39" s="17" t="n"/>
+      <c r="J39" s="21" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n">
+      <c r="A40" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="16">
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="20">
         <f>IF(OR($D40="",$E40=""),"",$E40-$D40+1)</f>
         <v/>
       </c>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="16">
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20">
         <f>IF(OR($B40="",$D40="",$E40=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B40)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B40&lt;&gt;"")*($G40&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="20">
         <f>IF($D40="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J40" s="17" t="n"/>
+      <c r="J40" s="21" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n">
+      <c r="A41" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="16">
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="25" t="n"/>
+      <c r="E41" s="25" t="n"/>
+      <c r="F41" s="20">
         <f>IF(OR($D41="",$E41=""),"",$E41-$D41+1)</f>
         <v/>
       </c>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="16">
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20">
         <f>IF(OR($B41="",$D41="",$E41=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B41)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B41&lt;&gt;"")*($G41&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="20">
         <f>IF($D41="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J41" s="17" t="n"/>
+      <c r="J41" s="21" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n">
+      <c r="A42" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="16">
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="25" t="n"/>
+      <c r="F42" s="20">
         <f>IF(OR($D42="",$E42=""),"",$E42-$D42+1)</f>
         <v/>
       </c>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="16">
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20">
         <f>IF(OR($B42="",$D42="",$E42=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B42)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B42&lt;&gt;"")*($G42&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="20">
         <f>IF($D42="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J42" s="17" t="n"/>
+      <c r="J42" s="21" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n">
+      <c r="A43" s="20" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="16">
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="20">
         <f>IF(OR($D43="",$E43=""),"",$E43-$D43+1)</f>
         <v/>
       </c>
-      <c r="G43" s="16" t="n"/>
-      <c r="H43" s="16">
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20">
         <f>IF(OR($B43="",$D43="",$E43=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B43)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B43&lt;&gt;"")*($G43&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="20">
         <f>IF($D43="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J43" s="17" t="n"/>
+      <c r="J43" s="21" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n">
+      <c r="A44" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="16">
+      <c r="B44" s="21" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="20">
         <f>IF(OR($D44="",$E44=""),"",$E44-$D44+1)</f>
         <v/>
       </c>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="16">
+      <c r="G44" s="20" t="n"/>
+      <c r="H44" s="20">
         <f>IF(OR($B44="",$D44="",$E44=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B44)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B44&lt;&gt;"")*($G44&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="20">
         <f>IF($D44="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J44" s="17" t="n"/>
+      <c r="J44" s="21" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n">
+      <c r="A45" s="20" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="16">
+      <c r="B45" s="21" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="20">
         <f>IF(OR($D45="",$E45=""),"",$E45-$D45+1)</f>
         <v/>
       </c>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="16">
+      <c r="G45" s="20" t="n"/>
+      <c r="H45" s="20">
         <f>IF(OR($B45="",$D45="",$E45=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B45)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B45&lt;&gt;"")*($G45&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="20">
         <f>IF($D45="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J45" s="17" t="n"/>
+      <c r="J45" s="21" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n">
+      <c r="A46" s="20" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="16">
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="25" t="n"/>
+      <c r="F46" s="20">
         <f>IF(OR($D46="",$E46=""),"",$E46-$D46+1)</f>
         <v/>
       </c>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="16">
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20">
         <f>IF(OR($B46="",$D46="",$E46=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B46)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B46&lt;&gt;"")*($G46&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="20">
         <f>IF($D46="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J46" s="17" t="n"/>
+      <c r="J46" s="21" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n">
+      <c r="A47" s="20" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="16">
+      <c r="B47" s="21" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="25" t="n"/>
+      <c r="E47" s="25" t="n"/>
+      <c r="F47" s="20">
         <f>IF(OR($D47="",$E47=""),"",$E47-$D47+1)</f>
         <v/>
       </c>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="16">
+      <c r="G47" s="20" t="n"/>
+      <c r="H47" s="20">
         <f>IF(OR($B47="",$D47="",$E47=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B47)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B47&lt;&gt;"")*($G47&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I47" s="16">
+      <c r="I47" s="20">
         <f>IF($D47="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J47" s="17" t="n"/>
+      <c r="J47" s="21" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n">
+      <c r="A48" s="20" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="16">
+      <c r="B48" s="21" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="25" t="n"/>
+      <c r="E48" s="25" t="n"/>
+      <c r="F48" s="20">
         <f>IF(OR($D48="",$E48=""),"",$E48-$D48+1)</f>
         <v/>
       </c>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="16">
+      <c r="G48" s="20" t="n"/>
+      <c r="H48" s="20">
         <f>IF(OR($B48="",$D48="",$E48=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B48)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B48&lt;&gt;"")*($G48&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="20">
         <f>IF($D48="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J48" s="17" t="n"/>
+      <c r="J48" s="21" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
+      <c r="A49" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="21" t="n"/>
-      <c r="F49" s="16">
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="20">
         <f>IF(OR($D49="",$E49=""),"",$E49-$D49+1)</f>
         <v/>
       </c>
-      <c r="G49" s="16" t="n"/>
-      <c r="H49" s="16">
+      <c r="G49" s="20" t="n"/>
+      <c r="H49" s="20">
         <f>IF(OR($B49="",$D49="",$E49=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B49)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B49&lt;&gt;"")*($G49&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="20">
         <f>IF($D49="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J49" s="17" t="n"/>
+      <c r="J49" s="21" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n">
+      <c r="A50" s="20" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="21" t="n"/>
-      <c r="F50" s="16">
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="20" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="25" t="n"/>
+      <c r="F50" s="20">
         <f>IF(OR($D50="",$E50=""),"",$E50-$D50+1)</f>
         <v/>
       </c>
-      <c r="G50" s="16" t="n"/>
-      <c r="H50" s="16">
+      <c r="G50" s="20" t="n"/>
+      <c r="H50" s="20">
         <f>IF(OR($B50="",$D50="",$E50=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B50)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B50&lt;&gt;"")*($G50&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="20">
         <f>IF($D50="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J50" s="17" t="n"/>
+      <c r="J50" s="21" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n">
+      <c r="A51" s="20" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="16">
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="20">
         <f>IF(OR($D51="",$E51=""),"",$E51-$D51+1)</f>
         <v/>
       </c>
-      <c r="G51" s="16" t="n"/>
-      <c r="H51" s="16">
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20">
         <f>IF(OR($B51="",$D51="",$E51=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B51)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B51&lt;&gt;"")*($G51&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="20">
         <f>IF($D51="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J51" s="17" t="n"/>
+      <c r="J51" s="21" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n">
+      <c r="A52" s="20" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="16">
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="25" t="n"/>
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="20">
         <f>IF(OR($D52="",$E52=""),"",$E52-$D52+1)</f>
         <v/>
       </c>
-      <c r="G52" s="16" t="n"/>
-      <c r="H52" s="16">
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="20">
         <f>IF(OR($B52="",$D52="",$E52=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B52)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B52&lt;&gt;"")*($G52&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="20">
         <f>IF($D52="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J52" s="17" t="n"/>
+      <c r="J52" s="21" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n">
+      <c r="A53" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="21" t="n"/>
-      <c r="F53" s="16">
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="25" t="n"/>
+      <c r="E53" s="25" t="n"/>
+      <c r="F53" s="20">
         <f>IF(OR($D53="",$E53=""),"",$E53-$D53+1)</f>
         <v/>
       </c>
-      <c r="G53" s="16" t="n"/>
-      <c r="H53" s="16">
+      <c r="G53" s="20" t="n"/>
+      <c r="H53" s="20">
         <f>IF(OR($B53="",$D53="",$E53=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B53)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B53&lt;&gt;"")*($G53&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="20">
         <f>IF($D53="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J53" s="17" t="n"/>
+      <c r="J53" s="21" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n">
+      <c r="A54" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="16">
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="20">
         <f>IF(OR($D54="",$E54=""),"",$E54-$D54+1)</f>
         <v/>
       </c>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="16">
+      <c r="G54" s="20" t="n"/>
+      <c r="H54" s="20">
         <f>IF(OR($B54="",$D54="",$E54=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B54)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B54&lt;&gt;"")*($G54&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I54" s="16">
+      <c r="I54" s="20">
         <f>IF($D54="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J54" s="17" t="n"/>
+      <c r="J54" s="21" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n">
+      <c r="A55" s="20" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="21" t="n"/>
-      <c r="E55" s="21" t="n"/>
-      <c r="F55" s="16">
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="25" t="n"/>
+      <c r="E55" s="25" t="n"/>
+      <c r="F55" s="20">
         <f>IF(OR($D55="",$E55=""),"",$E55-$D55+1)</f>
         <v/>
       </c>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="16">
+      <c r="G55" s="20" t="n"/>
+      <c r="H55" s="20">
         <f>IF(OR($B55="",$D55="",$E55=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B55)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B55&lt;&gt;"")*($G55&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I55" s="16">
+      <c r="I55" s="20">
         <f>IF($D55="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J55" s="17" t="n"/>
+      <c r="J55" s="21" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n">
+      <c r="A56" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="21" t="n"/>
-      <c r="F56" s="16">
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="25" t="n"/>
+      <c r="E56" s="25" t="n"/>
+      <c r="F56" s="20">
         <f>IF(OR($D56="",$E56=""),"",$E56-$D56+1)</f>
         <v/>
       </c>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="16">
+      <c r="G56" s="20" t="n"/>
+      <c r="H56" s="20">
         <f>IF(OR($B56="",$D56="",$E56=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B56)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B56&lt;&gt;"")*($G56&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I56" s="16">
+      <c r="I56" s="20">
         <f>IF($D56="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J56" s="17" t="n"/>
+      <c r="J56" s="21" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n">
+      <c r="A57" s="20" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="16" t="n"/>
-      <c r="D57" s="21" t="n"/>
-      <c r="E57" s="21" t="n"/>
-      <c r="F57" s="16">
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="25" t="n"/>
+      <c r="E57" s="25" t="n"/>
+      <c r="F57" s="20">
         <f>IF(OR($D57="",$E57=""),"",$E57-$D57+1)</f>
         <v/>
       </c>
-      <c r="G57" s="16" t="n"/>
-      <c r="H57" s="16">
+      <c r="G57" s="20" t="n"/>
+      <c r="H57" s="20">
         <f>IF(OR($B57="",$D57="",$E57=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B57)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B57&lt;&gt;"")*($G57&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I57" s="16">
+      <c r="I57" s="20">
         <f>IF($D57="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J57" s="17" t="n"/>
+      <c r="J57" s="21" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n">
+      <c r="A58" s="20" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="16" t="n"/>
-      <c r="D58" s="21" t="n"/>
-      <c r="E58" s="21" t="n"/>
-      <c r="F58" s="16">
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="25" t="n"/>
+      <c r="E58" s="25" t="n"/>
+      <c r="F58" s="20">
         <f>IF(OR($D58="",$E58=""),"",$E58-$D58+1)</f>
         <v/>
       </c>
-      <c r="G58" s="16" t="n"/>
-      <c r="H58" s="16">
+      <c r="G58" s="20" t="n"/>
+      <c r="H58" s="20">
         <f>IF(OR($B58="",$D58="",$E58=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B58)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B58&lt;&gt;"")*($G58&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I58" s="16">
+      <c r="I58" s="20">
         <f>IF($D58="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J58" s="17" t="n"/>
+      <c r="J58" s="21" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n">
+      <c r="A59" s="20" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="17" t="n"/>
-      <c r="C59" s="16" t="n"/>
-      <c r="D59" s="21" t="n"/>
-      <c r="E59" s="21" t="n"/>
-      <c r="F59" s="16">
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="25" t="n"/>
+      <c r="E59" s="25" t="n"/>
+      <c r="F59" s="20">
         <f>IF(OR($D59="",$E59=""),"",$E59-$D59+1)</f>
         <v/>
       </c>
-      <c r="G59" s="16" t="n"/>
-      <c r="H59" s="16">
+      <c r="G59" s="20" t="n"/>
+      <c r="H59" s="20">
         <f>IF(OR($B59="",$D59="",$E59=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B59)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B59&lt;&gt;"")*($G59&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I59" s="16">
+      <c r="I59" s="20">
         <f>IF($D59="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J59" s="17" t="n"/>
+      <c r="J59" s="21" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n">
+      <c r="A60" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="17" t="n"/>
-      <c r="C60" s="16" t="n"/>
-      <c r="D60" s="21" t="n"/>
-      <c r="E60" s="21" t="n"/>
-      <c r="F60" s="16">
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="25" t="n"/>
+      <c r="E60" s="25" t="n"/>
+      <c r="F60" s="20">
         <f>IF(OR($D60="",$E60=""),"",$E60-$D60+1)</f>
         <v/>
       </c>
-      <c r="G60" s="16" t="n"/>
-      <c r="H60" s="16">
+      <c r="G60" s="20" t="n"/>
+      <c r="H60" s="20">
         <f>IF(OR($B60="",$D60="",$E60=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B60)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B60&lt;&gt;"")*($G60&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I60" s="16">
+      <c r="I60" s="20">
         <f>IF($D60="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J60" s="17" t="n"/>
+      <c r="J60" s="21" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n">
+      <c r="A61" s="20" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="16" t="n"/>
-      <c r="D61" s="21" t="n"/>
-      <c r="E61" s="21" t="n"/>
-      <c r="F61" s="16">
+      <c r="B61" s="21" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="25" t="n"/>
+      <c r="E61" s="25" t="n"/>
+      <c r="F61" s="20">
         <f>IF(OR($D61="",$E61=""),"",$E61-$D61+1)</f>
         <v/>
       </c>
-      <c r="G61" s="16" t="n"/>
-      <c r="H61" s="16">
+      <c r="G61" s="20" t="n"/>
+      <c r="H61" s="20">
         <f>IF(OR($B61="",$D61="",$E61=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B61)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B61&lt;&gt;"")*($G61&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I61" s="16">
+      <c r="I61" s="20">
         <f>IF($D61="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J61" s="17" t="n"/>
+      <c r="J61" s="21" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n">
+      <c r="A62" s="20" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="17" t="n"/>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="21" t="n"/>
-      <c r="E62" s="21" t="n"/>
-      <c r="F62" s="16">
+      <c r="B62" s="21" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="25" t="n"/>
+      <c r="E62" s="25" t="n"/>
+      <c r="F62" s="20">
         <f>IF(OR($D62="",$E62=""),"",$E62-$D62+1)</f>
         <v/>
       </c>
-      <c r="G62" s="16" t="n"/>
-      <c r="H62" s="16">
+      <c r="G62" s="20" t="n"/>
+      <c r="H62" s="20">
         <f>IF(OR($B62="",$D62="",$E62=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B62)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B62&lt;&gt;"")*($G62&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I62" s="16">
+      <c r="I62" s="20">
         <f>IF($D62="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J62" s="17" t="n"/>
+      <c r="J62" s="21" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n">
+      <c r="A63" s="20" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="17" t="n"/>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="21" t="n"/>
-      <c r="E63" s="21" t="n"/>
-      <c r="F63" s="16">
+      <c r="B63" s="21" t="n"/>
+      <c r="C63" s="20" t="n"/>
+      <c r="D63" s="25" t="n"/>
+      <c r="E63" s="25" t="n"/>
+      <c r="F63" s="20">
         <f>IF(OR($D63="",$E63=""),"",$E63-$D63+1)</f>
         <v/>
       </c>
-      <c r="G63" s="16" t="n"/>
-      <c r="H63" s="16">
+      <c r="G63" s="20" t="n"/>
+      <c r="H63" s="20">
         <f>IF(OR($B63="",$D63="",$E63=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B63)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B63&lt;&gt;"")*($G63&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I63" s="16">
+      <c r="I63" s="20">
         <f>IF($D63="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J63" s="17" t="n"/>
+      <c r="J63" s="21" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n">
+      <c r="A64" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="21" t="n"/>
-      <c r="E64" s="21" t="n"/>
-      <c r="F64" s="16">
+      <c r="B64" s="21" t="n"/>
+      <c r="C64" s="20" t="n"/>
+      <c r="D64" s="25" t="n"/>
+      <c r="E64" s="25" t="n"/>
+      <c r="F64" s="20">
         <f>IF(OR($D64="",$E64=""),"",$E64-$D64+1)</f>
         <v/>
       </c>
-      <c r="G64" s="16" t="n"/>
-      <c r="H64" s="16">
+      <c r="G64" s="20" t="n"/>
+      <c r="H64" s="20">
         <f>IF(OR($B64="",$D64="",$E64=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B64)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B64&lt;&gt;"")*($G64&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I64" s="16">
+      <c r="I64" s="20">
         <f>IF($D64="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J64" s="17" t="n"/>
+      <c r="J64" s="21" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n">
+      <c r="A65" s="20" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="17" t="n"/>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="16">
+      <c r="B65" s="21" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="25" t="n"/>
+      <c r="E65" s="25" t="n"/>
+      <c r="F65" s="20">
         <f>IF(OR($D65="",$E65=""),"",$E65-$D65+1)</f>
         <v/>
       </c>
-      <c r="G65" s="16" t="n"/>
-      <c r="H65" s="16">
+      <c r="G65" s="20" t="n"/>
+      <c r="H65" s="20">
         <f>IF(OR($B65="",$D65="",$E65=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B65)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B65&lt;&gt;"")*($G65&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I65" s="16">
+      <c r="I65" s="20">
         <f>IF($D65="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J65" s="17" t="n"/>
+      <c r="J65" s="21" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n">
+      <c r="A66" s="20" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="17" t="n"/>
-      <c r="C66" s="16" t="n"/>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="16">
+      <c r="B66" s="21" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="25" t="n"/>
+      <c r="E66" s="25" t="n"/>
+      <c r="F66" s="20">
         <f>IF(OR($D66="",$E66=""),"",$E66-$D66+1)</f>
         <v/>
       </c>
-      <c r="G66" s="16" t="n"/>
-      <c r="H66" s="16">
+      <c r="G66" s="20" t="n"/>
+      <c r="H66" s="20">
         <f>IF(OR($B66="",$D66="",$E66=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B66)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B66&lt;&gt;"")*($G66&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I66" s="16">
+      <c r="I66" s="20">
         <f>IF($D66="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J66" s="17" t="n"/>
+      <c r="J66" s="21" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n">
+      <c r="A67" s="20" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="17" t="n"/>
-      <c r="C67" s="16" t="n"/>
-      <c r="D67" s="21" t="n"/>
-      <c r="E67" s="21" t="n"/>
-      <c r="F67" s="16">
+      <c r="B67" s="21" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="25" t="n"/>
+      <c r="E67" s="25" t="n"/>
+      <c r="F67" s="20">
         <f>IF(OR($D67="",$E67=""),"",$E67-$D67+1)</f>
         <v/>
       </c>
-      <c r="G67" s="16" t="n"/>
-      <c r="H67" s="16">
+      <c r="G67" s="20" t="n"/>
+      <c r="H67" s="20">
         <f>IF(OR($B67="",$D67="",$E67=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B67)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B67&lt;&gt;"")*($G67&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I67" s="16">
+      <c r="I67" s="20">
         <f>IF($D67="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J67" s="17" t="n"/>
+      <c r="J67" s="21" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n">
+      <c r="A68" s="20" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="17" t="n"/>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="F68" s="16">
+      <c r="B68" s="21" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="25" t="n"/>
+      <c r="E68" s="25" t="n"/>
+      <c r="F68" s="20">
         <f>IF(OR($D68="",$E68=""),"",$E68-$D68+1)</f>
         <v/>
       </c>
-      <c r="G68" s="16" t="n"/>
-      <c r="H68" s="16">
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="20">
         <f>IF(OR($B68="",$D68="",$E68=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B68)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B68&lt;&gt;"")*($G68&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I68" s="16">
+      <c r="I68" s="20">
         <f>IF($D68="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J68" s="17" t="n"/>
+      <c r="J68" s="21" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n">
+      <c r="A69" s="20" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="17" t="n"/>
-      <c r="C69" s="16" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="16">
+      <c r="B69" s="21" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="25" t="n"/>
+      <c r="E69" s="25" t="n"/>
+      <c r="F69" s="20">
         <f>IF(OR($D69="",$E69=""),"",$E69-$D69+1)</f>
         <v/>
       </c>
-      <c r="G69" s="16" t="n"/>
-      <c r="H69" s="16">
+      <c r="G69" s="20" t="n"/>
+      <c r="H69" s="20">
         <f>IF(OR($B69="",$D69="",$E69=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B69)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B69&lt;&gt;"")*($G69&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I69" s="16">
+      <c r="I69" s="20">
         <f>IF($D69="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J69" s="17" t="n"/>
+      <c r="J69" s="21" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n">
+      <c r="A70" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="17" t="n"/>
-      <c r="C70" s="16" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="16">
+      <c r="B70" s="21" t="n"/>
+      <c r="C70" s="20" t="n"/>
+      <c r="D70" s="25" t="n"/>
+      <c r="E70" s="25" t="n"/>
+      <c r="F70" s="20">
         <f>IF(OR($D70="",$E70=""),"",$E70-$D70+1)</f>
         <v/>
       </c>
-      <c r="G70" s="16" t="n"/>
-      <c r="H70" s="16">
+      <c r="G70" s="20" t="n"/>
+      <c r="H70" s="20">
         <f>IF(OR($B70="",$D70="",$E70=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B70)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B70&lt;&gt;"")*($G70&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I70" s="16">
+      <c r="I70" s="20">
         <f>IF($D70="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J70" s="17" t="n"/>
+      <c r="J70" s="21" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n">
+      <c r="A71" s="20" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="16" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="16">
+      <c r="B71" s="21" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="25" t="n"/>
+      <c r="E71" s="25" t="n"/>
+      <c r="F71" s="20">
         <f>IF(OR($D71="",$E71=""),"",$E71-$D71+1)</f>
         <v/>
       </c>
-      <c r="G71" s="16" t="n"/>
-      <c r="H71" s="16">
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20">
         <f>IF(OR($B71="",$D71="",$E71=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B71)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B71&lt;&gt;"")*($G71&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I71" s="16">
+      <c r="I71" s="20">
         <f>IF($D71="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J71" s="17" t="n"/>
+      <c r="J71" s="21" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n">
+      <c r="A72" s="20" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="17" t="n"/>
-      <c r="C72" s="16" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="16">
+      <c r="B72" s="21" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="25" t="n"/>
+      <c r="E72" s="25" t="n"/>
+      <c r="F72" s="20">
         <f>IF(OR($D72="",$E72=""),"",$E72-$D72+1)</f>
         <v/>
       </c>
-      <c r="G72" s="16" t="n"/>
-      <c r="H72" s="16">
+      <c r="G72" s="20" t="n"/>
+      <c r="H72" s="20">
         <f>IF(OR($B72="",$D72="",$E72=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B72)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B72&lt;&gt;"")*($G72&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I72" s="16">
+      <c r="I72" s="20">
         <f>IF($D72="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J72" s="17" t="n"/>
+      <c r="J72" s="21" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n">
+      <c r="A73" s="20" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="16" t="n"/>
-      <c r="D73" s="21" t="n"/>
-      <c r="E73" s="21" t="n"/>
-      <c r="F73" s="16">
+      <c r="B73" s="21" t="n"/>
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="25" t="n"/>
+      <c r="E73" s="25" t="n"/>
+      <c r="F73" s="20">
         <f>IF(OR($D73="",$E73=""),"",$E73-$D73+1)</f>
         <v/>
       </c>
-      <c r="G73" s="16" t="n"/>
-      <c r="H73" s="16">
+      <c r="G73" s="20" t="n"/>
+      <c r="H73" s="20">
         <f>IF(OR($B73="",$D73="",$E73=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B73)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B73&lt;&gt;"")*($G73&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I73" s="16">
+      <c r="I73" s="20">
         <f>IF($D73="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J73" s="17" t="n"/>
+      <c r="J73" s="21" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n">
+      <c r="A74" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="17" t="n"/>
-      <c r="C74" s="16" t="n"/>
-      <c r="D74" s="21" t="n"/>
-      <c r="E74" s="21" t="n"/>
-      <c r="F74" s="16">
+      <c r="B74" s="21" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="25" t="n"/>
+      <c r="E74" s="25" t="n"/>
+      <c r="F74" s="20">
         <f>IF(OR($D74="",$E74=""),"",$E74-$D74+1)</f>
         <v/>
       </c>
-      <c r="G74" s="16" t="n"/>
-      <c r="H74" s="16">
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="20">
         <f>IF(OR($B74="",$D74="",$E74=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B74)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B74&lt;&gt;"")*($G74&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I74" s="16">
+      <c r="I74" s="20">
         <f>IF($D74="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J74" s="17" t="n"/>
+      <c r="J74" s="21" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n">
+      <c r="A75" s="20" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="17" t="n"/>
-      <c r="C75" s="16" t="n"/>
-      <c r="D75" s="21" t="n"/>
-      <c r="E75" s="21" t="n"/>
-      <c r="F75" s="16">
+      <c r="B75" s="21" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="25" t="n"/>
+      <c r="E75" s="25" t="n"/>
+      <c r="F75" s="20">
         <f>IF(OR($D75="",$E75=""),"",$E75-$D75+1)</f>
         <v/>
       </c>
-      <c r="G75" s="16" t="n"/>
-      <c r="H75" s="16">
+      <c r="G75" s="20" t="n"/>
+      <c r="H75" s="20">
         <f>IF(OR($B75="",$D75="",$E75=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B75)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B75&lt;&gt;"")*($G75&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I75" s="16">
+      <c r="I75" s="20">
         <f>IF($D75="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J75" s="17" t="n"/>
+      <c r="J75" s="21" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n">
+      <c r="A76" s="20" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="17" t="n"/>
-      <c r="C76" s="16" t="n"/>
-      <c r="D76" s="21" t="n"/>
-      <c r="E76" s="21" t="n"/>
-      <c r="F76" s="16">
+      <c r="B76" s="21" t="n"/>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="25" t="n"/>
+      <c r="E76" s="25" t="n"/>
+      <c r="F76" s="20">
         <f>IF(OR($D76="",$E76=""),"",$E76-$D76+1)</f>
         <v/>
       </c>
-      <c r="G76" s="16" t="n"/>
-      <c r="H76" s="16">
+      <c r="G76" s="20" t="n"/>
+      <c r="H76" s="20">
         <f>IF(OR($B76="",$D76="",$E76=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B76)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B76&lt;&gt;"")*($G76&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I76" s="16">
+      <c r="I76" s="20">
         <f>IF($D76="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J76" s="17" t="n"/>
+      <c r="J76" s="21" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n">
+      <c r="A77" s="20" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="17" t="n"/>
-      <c r="C77" s="16" t="n"/>
-      <c r="D77" s="21" t="n"/>
-      <c r="E77" s="21" t="n"/>
-      <c r="F77" s="16">
+      <c r="B77" s="21" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="25" t="n"/>
+      <c r="E77" s="25" t="n"/>
+      <c r="F77" s="20">
         <f>IF(OR($D77="",$E77=""),"",$E77-$D77+1)</f>
         <v/>
       </c>
-      <c r="G77" s="16" t="n"/>
-      <c r="H77" s="16">
+      <c r="G77" s="20" t="n"/>
+      <c r="H77" s="20">
         <f>IF(OR($B77="",$D77="",$E77=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B77)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B77&lt;&gt;"")*($G77&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I77" s="16">
+      <c r="I77" s="20">
         <f>IF($D77="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J77" s="17" t="n"/>
+      <c r="J77" s="21" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n">
+      <c r="A78" s="20" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="17" t="n"/>
-      <c r="C78" s="16" t="n"/>
-      <c r="D78" s="21" t="n"/>
-      <c r="E78" s="21" t="n"/>
-      <c r="F78" s="16">
+      <c r="B78" s="21" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="25" t="n"/>
+      <c r="E78" s="25" t="n"/>
+      <c r="F78" s="20">
         <f>IF(OR($D78="",$E78=""),"",$E78-$D78+1)</f>
         <v/>
       </c>
-      <c r="G78" s="16" t="n"/>
-      <c r="H78" s="16">
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20">
         <f>IF(OR($B78="",$D78="",$E78=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B78)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B78&lt;&gt;"")*($G78&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I78" s="16">
+      <c r="I78" s="20">
         <f>IF($D78="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J78" s="17" t="n"/>
+      <c r="J78" s="21" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n">
+      <c r="A79" s="20" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="17" t="n"/>
-      <c r="C79" s="16" t="n"/>
-      <c r="D79" s="21" t="n"/>
-      <c r="E79" s="21" t="n"/>
-      <c r="F79" s="16">
+      <c r="B79" s="21" t="n"/>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="25" t="n"/>
+      <c r="E79" s="25" t="n"/>
+      <c r="F79" s="20">
         <f>IF(OR($D79="",$E79=""),"",$E79-$D79+1)</f>
         <v/>
       </c>
-      <c r="G79" s="16" t="n"/>
-      <c r="H79" s="16">
+      <c r="G79" s="20" t="n"/>
+      <c r="H79" s="20">
         <f>IF(OR($B79="",$D79="",$E79=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B79)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B79&lt;&gt;"")*($G79&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I79" s="16">
+      <c r="I79" s="20">
         <f>IF($D79="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J79" s="17" t="n"/>
+      <c r="J79" s="21" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n">
+      <c r="A80" s="20" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="17" t="n"/>
-      <c r="C80" s="16" t="n"/>
-      <c r="D80" s="21" t="n"/>
-      <c r="E80" s="21" t="n"/>
-      <c r="F80" s="16">
+      <c r="B80" s="21" t="n"/>
+      <c r="C80" s="20" t="n"/>
+      <c r="D80" s="25" t="n"/>
+      <c r="E80" s="25" t="n"/>
+      <c r="F80" s="20">
         <f>IF(OR($D80="",$E80=""),"",$E80-$D80+1)</f>
         <v/>
       </c>
-      <c r="G80" s="16" t="n"/>
-      <c r="H80" s="16">
+      <c r="G80" s="20" t="n"/>
+      <c r="H80" s="20">
         <f>IF(OR($B80="",$D80="",$E80=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B80)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B80&lt;&gt;"")*($G80&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I80" s="16">
+      <c r="I80" s="20">
         <f>IF($D80="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J80" s="17" t="n"/>
+      <c r="J80" s="21" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n">
+      <c r="A81" s="20" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="17" t="n"/>
-      <c r="C81" s="16" t="n"/>
-      <c r="D81" s="21" t="n"/>
-      <c r="E81" s="21" t="n"/>
-      <c r="F81" s="16">
+      <c r="B81" s="21" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="25" t="n"/>
+      <c r="E81" s="25" t="n"/>
+      <c r="F81" s="20">
         <f>IF(OR($D81="",$E81=""),"",$E81-$D81+1)</f>
         <v/>
       </c>
-      <c r="G81" s="16" t="n"/>
-      <c r="H81" s="16">
+      <c r="G81" s="20" t="n"/>
+      <c r="H81" s="20">
         <f>IF(OR($B81="",$D81="",$E81=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B81)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B81&lt;&gt;"")*($G81&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I81" s="16">
+      <c r="I81" s="20">
         <f>IF($D81="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J81" s="17" t="n"/>
+      <c r="J81" s="21" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n">
+      <c r="A82" s="20" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="17" t="n"/>
-      <c r="C82" s="16" t="n"/>
-      <c r="D82" s="21" t="n"/>
-      <c r="E82" s="21" t="n"/>
-      <c r="F82" s="16">
+      <c r="B82" s="21" t="n"/>
+      <c r="C82" s="20" t="n"/>
+      <c r="D82" s="25" t="n"/>
+      <c r="E82" s="25" t="n"/>
+      <c r="F82" s="20">
         <f>IF(OR($D82="",$E82=""),"",$E82-$D82+1)</f>
         <v/>
       </c>
-      <c r="G82" s="16" t="n"/>
-      <c r="H82" s="16">
+      <c r="G82" s="20" t="n"/>
+      <c r="H82" s="20">
         <f>IF(OR($B82="",$D82="",$E82=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B82)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B82&lt;&gt;"")*($G82&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I82" s="16">
+      <c r="I82" s="20">
         <f>IF($D82="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J82" s="17" t="n"/>
+      <c r="J82" s="21" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n">
+      <c r="A83" s="20" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="17" t="n"/>
-      <c r="C83" s="16" t="n"/>
-      <c r="D83" s="21" t="n"/>
-      <c r="E83" s="21" t="n"/>
-      <c r="F83" s="16">
+      <c r="B83" s="21" t="n"/>
+      <c r="C83" s="20" t="n"/>
+      <c r="D83" s="25" t="n"/>
+      <c r="E83" s="25" t="n"/>
+      <c r="F83" s="20">
         <f>IF(OR($D83="",$E83=""),"",$E83-$D83+1)</f>
         <v/>
       </c>
-      <c r="G83" s="16" t="n"/>
-      <c r="H83" s="16">
+      <c r="G83" s="20" t="n"/>
+      <c r="H83" s="20">
         <f>IF(OR($B83="",$D83="",$E83=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B83)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B83&lt;&gt;"")*($G83&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I83" s="16">
+      <c r="I83" s="20">
         <f>IF($D83="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J83" s="17" t="n"/>
+      <c r="J83" s="21" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n">
+      <c r="A84" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="17" t="n"/>
-      <c r="C84" s="16" t="n"/>
-      <c r="D84" s="21" t="n"/>
-      <c r="E84" s="21" t="n"/>
-      <c r="F84" s="16">
+      <c r="B84" s="21" t="n"/>
+      <c r="C84" s="20" t="n"/>
+      <c r="D84" s="25" t="n"/>
+      <c r="E84" s="25" t="n"/>
+      <c r="F84" s="20">
         <f>IF(OR($D84="",$E84=""),"",$E84-$D84+1)</f>
         <v/>
       </c>
-      <c r="G84" s="16" t="n"/>
-      <c r="H84" s="16">
+      <c r="G84" s="20" t="n"/>
+      <c r="H84" s="20">
         <f>IF(OR($B84="",$D84="",$E84=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B84)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B84&lt;&gt;"")*($G84&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I84" s="16">
+      <c r="I84" s="20">
         <f>IF($D84="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J84" s="17" t="n"/>
+      <c r="J84" s="21" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n">
+      <c r="A85" s="20" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="17" t="n"/>
-      <c r="C85" s="16" t="n"/>
-      <c r="D85" s="21" t="n"/>
-      <c r="E85" s="21" t="n"/>
-      <c r="F85" s="16">
+      <c r="B85" s="21" t="n"/>
+      <c r="C85" s="20" t="n"/>
+      <c r="D85" s="25" t="n"/>
+      <c r="E85" s="25" t="n"/>
+      <c r="F85" s="20">
         <f>IF(OR($D85="",$E85=""),"",$E85-$D85+1)</f>
         <v/>
       </c>
-      <c r="G85" s="16" t="n"/>
-      <c r="H85" s="16">
+      <c r="G85" s="20" t="n"/>
+      <c r="H85" s="20">
         <f>IF(OR($B85="",$D85="",$E85=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B85)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B85&lt;&gt;"")*($G85&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I85" s="16">
+      <c r="I85" s="20">
         <f>IF($D85="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J85" s="17" t="n"/>
+      <c r="J85" s="21" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n">
+      <c r="A86" s="20" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="17" t="n"/>
-      <c r="C86" s="16" t="n"/>
-      <c r="D86" s="21" t="n"/>
-      <c r="E86" s="21" t="n"/>
-      <c r="F86" s="16">
+      <c r="B86" s="21" t="n"/>
+      <c r="C86" s="20" t="n"/>
+      <c r="D86" s="25" t="n"/>
+      <c r="E86" s="25" t="n"/>
+      <c r="F86" s="20">
         <f>IF(OR($D86="",$E86=""),"",$E86-$D86+1)</f>
         <v/>
       </c>
-      <c r="G86" s="16" t="n"/>
-      <c r="H86" s="16">
+      <c r="G86" s="20" t="n"/>
+      <c r="H86" s="20">
         <f>IF(OR($B86="",$D86="",$E86=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B86)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B86&lt;&gt;"")*($G86&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I86" s="16">
+      <c r="I86" s="20">
         <f>IF($D86="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J86" s="17" t="n"/>
+      <c r="J86" s="21" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n">
+      <c r="A87" s="20" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="17" t="n"/>
-      <c r="C87" s="16" t="n"/>
-      <c r="D87" s="21" t="n"/>
-      <c r="E87" s="21" t="n"/>
-      <c r="F87" s="16">
+      <c r="B87" s="21" t="n"/>
+      <c r="C87" s="20" t="n"/>
+      <c r="D87" s="25" t="n"/>
+      <c r="E87" s="25" t="n"/>
+      <c r="F87" s="20">
         <f>IF(OR($D87="",$E87=""),"",$E87-$D87+1)</f>
         <v/>
       </c>
-      <c r="G87" s="16" t="n"/>
-      <c r="H87" s="16">
+      <c r="G87" s="20" t="n"/>
+      <c r="H87" s="20">
         <f>IF(OR($B87="",$D87="",$E87=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B87)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B87&lt;&gt;"")*($G87&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I87" s="16">
+      <c r="I87" s="20">
         <f>IF($D87="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J87" s="17" t="n"/>
+      <c r="J87" s="21" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n">
+      <c r="A88" s="20" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="17" t="n"/>
-      <c r="C88" s="16" t="n"/>
-      <c r="D88" s="21" t="n"/>
-      <c r="E88" s="21" t="n"/>
-      <c r="F88" s="16">
+      <c r="B88" s="21" t="n"/>
+      <c r="C88" s="20" t="n"/>
+      <c r="D88" s="25" t="n"/>
+      <c r="E88" s="25" t="n"/>
+      <c r="F88" s="20">
         <f>IF(OR($D88="",$E88=""),"",$E88-$D88+1)</f>
         <v/>
       </c>
-      <c r="G88" s="16" t="n"/>
-      <c r="H88" s="16">
+      <c r="G88" s="20" t="n"/>
+      <c r="H88" s="20">
         <f>IF(OR($B88="",$D88="",$E88=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B88)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B88&lt;&gt;"")*($G88&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I88" s="16">
+      <c r="I88" s="20">
         <f>IF($D88="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J88" s="17" t="n"/>
+      <c r="J88" s="21" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n">
+      <c r="A89" s="20" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="17" t="n"/>
-      <c r="C89" s="16" t="n"/>
-      <c r="D89" s="21" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="16">
+      <c r="B89" s="21" t="n"/>
+      <c r="C89" s="20" t="n"/>
+      <c r="D89" s="25" t="n"/>
+      <c r="E89" s="25" t="n"/>
+      <c r="F89" s="20">
         <f>IF(OR($D89="",$E89=""),"",$E89-$D89+1)</f>
         <v/>
       </c>
-      <c r="G89" s="16" t="n"/>
-      <c r="H89" s="16">
+      <c r="G89" s="20" t="n"/>
+      <c r="H89" s="20">
         <f>IF(OR($B89="",$D89="",$E89=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B89)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B89&lt;&gt;"")*($G89&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I89" s="16">
+      <c r="I89" s="20">
         <f>IF($D89="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J89" s="17" t="n"/>
+      <c r="J89" s="21" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n">
+      <c r="A90" s="20" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="17" t="n"/>
-      <c r="C90" s="16" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="16">
+      <c r="B90" s="21" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="25" t="n"/>
+      <c r="E90" s="25" t="n"/>
+      <c r="F90" s="20">
         <f>IF(OR($D90="",$E90=""),"",$E90-$D90+1)</f>
         <v/>
       </c>
-      <c r="G90" s="16" t="n"/>
-      <c r="H90" s="16">
+      <c r="G90" s="20" t="n"/>
+      <c r="H90" s="20">
         <f>IF(OR($B90="",$D90="",$E90=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B90)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B90&lt;&gt;"")*($G90&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I90" s="16">
+      <c r="I90" s="20">
         <f>IF($D90="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J90" s="17" t="n"/>
+      <c r="J90" s="21" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n">
+      <c r="A91" s="20" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="17" t="n"/>
-      <c r="C91" s="16" t="n"/>
-      <c r="D91" s="21" t="n"/>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="16">
+      <c r="B91" s="21" t="n"/>
+      <c r="C91" s="20" t="n"/>
+      <c r="D91" s="25" t="n"/>
+      <c r="E91" s="25" t="n"/>
+      <c r="F91" s="20">
         <f>IF(OR($D91="",$E91=""),"",$E91-$D91+1)</f>
         <v/>
       </c>
-      <c r="G91" s="16" t="n"/>
-      <c r="H91" s="16">
+      <c r="G91" s="20" t="n"/>
+      <c r="H91" s="20">
         <f>IF(OR($B91="",$D91="",$E91=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B91)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B91&lt;&gt;"")*($G91&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I91" s="16">
+      <c r="I91" s="20">
         <f>IF($D91="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J91" s="17" t="n"/>
+      <c r="J91" s="21" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n">
+      <c r="A92" s="20" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="17" t="n"/>
-      <c r="C92" s="16" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="16">
+      <c r="B92" s="21" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="25" t="n"/>
+      <c r="E92" s="25" t="n"/>
+      <c r="F92" s="20">
         <f>IF(OR($D92="",$E92=""),"",$E92-$D92+1)</f>
         <v/>
       </c>
-      <c r="G92" s="16" t="n"/>
-      <c r="H92" s="16">
+      <c r="G92" s="20" t="n"/>
+      <c r="H92" s="20">
         <f>IF(OR($B92="",$D92="",$E92=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B92)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B92&lt;&gt;"")*($G92&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I92" s="16">
+      <c r="I92" s="20">
         <f>IF($D92="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J92" s="17" t="n"/>
+      <c r="J92" s="21" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n">
+      <c r="A93" s="20" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="17" t="n"/>
-      <c r="C93" s="16" t="n"/>
-      <c r="D93" s="21" t="n"/>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="16">
+      <c r="B93" s="21" t="n"/>
+      <c r="C93" s="20" t="n"/>
+      <c r="D93" s="25" t="n"/>
+      <c r="E93" s="25" t="n"/>
+      <c r="F93" s="20">
         <f>IF(OR($D93="",$E93=""),"",$E93-$D93+1)</f>
         <v/>
       </c>
-      <c r="G93" s="16" t="n"/>
-      <c r="H93" s="16">
+      <c r="G93" s="20" t="n"/>
+      <c r="H93" s="20">
         <f>IF(OR($B93="",$D93="",$E93=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B93)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B93&lt;&gt;"")*($G93&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I93" s="16">
+      <c r="I93" s="20">
         <f>IF($D93="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J93" s="17" t="n"/>
+      <c r="J93" s="21" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n">
+      <c r="A94" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="17" t="n"/>
-      <c r="C94" s="16" t="n"/>
-      <c r="D94" s="21" t="n"/>
-      <c r="E94" s="21" t="n"/>
-      <c r="F94" s="16">
+      <c r="B94" s="21" t="n"/>
+      <c r="C94" s="20" t="n"/>
+      <c r="D94" s="25" t="n"/>
+      <c r="E94" s="25" t="n"/>
+      <c r="F94" s="20">
         <f>IF(OR($D94="",$E94=""),"",$E94-$D94+1)</f>
         <v/>
       </c>
-      <c r="G94" s="16" t="n"/>
-      <c r="H94" s="16">
+      <c r="G94" s="20" t="n"/>
+      <c r="H94" s="20">
         <f>IF(OR($B94="",$D94="",$E94=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B94)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B94&lt;&gt;"")*($G94&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I94" s="16">
+      <c r="I94" s="20">
         <f>IF($D94="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J94" s="17" t="n"/>
+      <c r="J94" s="21" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n">
+      <c r="A95" s="20" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="17" t="n"/>
-      <c r="C95" s="16" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="16">
+      <c r="B95" s="21" t="n"/>
+      <c r="C95" s="20" t="n"/>
+      <c r="D95" s="25" t="n"/>
+      <c r="E95" s="25" t="n"/>
+      <c r="F95" s="20">
         <f>IF(OR($D95="",$E95=""),"",$E95-$D95+1)</f>
         <v/>
       </c>
-      <c r="G95" s="16" t="n"/>
-      <c r="H95" s="16">
+      <c r="G95" s="20" t="n"/>
+      <c r="H95" s="20">
         <f>IF(OR($B95="",$D95="",$E95=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B95)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B95&lt;&gt;"")*($G95&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I95" s="16">
+      <c r="I95" s="20">
         <f>IF($D95="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J95" s="17" t="n"/>
+      <c r="J95" s="21" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n">
+      <c r="A96" s="20" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="17" t="n"/>
-      <c r="C96" s="16" t="n"/>
-      <c r="D96" s="21" t="n"/>
-      <c r="E96" s="21" t="n"/>
-      <c r="F96" s="16">
+      <c r="B96" s="21" t="n"/>
+      <c r="C96" s="20" t="n"/>
+      <c r="D96" s="25" t="n"/>
+      <c r="E96" s="25" t="n"/>
+      <c r="F96" s="20">
         <f>IF(OR($D96="",$E96=""),"",$E96-$D96+1)</f>
         <v/>
       </c>
-      <c r="G96" s="16" t="n"/>
-      <c r="H96" s="16">
+      <c r="G96" s="20" t="n"/>
+      <c r="H96" s="20">
         <f>IF(OR($B96="",$D96="",$E96=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B96)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B96&lt;&gt;"")*($G96&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I96" s="16">
+      <c r="I96" s="20">
         <f>IF($D96="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J96" s="17" t="n"/>
+      <c r="J96" s="21" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n">
+      <c r="A97" s="20" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="17" t="n"/>
-      <c r="C97" s="16" t="n"/>
-      <c r="D97" s="21" t="n"/>
-      <c r="E97" s="21" t="n"/>
-      <c r="F97" s="16">
+      <c r="B97" s="21" t="n"/>
+      <c r="C97" s="20" t="n"/>
+      <c r="D97" s="25" t="n"/>
+      <c r="E97" s="25" t="n"/>
+      <c r="F97" s="20">
         <f>IF(OR($D97="",$E97=""),"",$E97-$D97+1)</f>
         <v/>
       </c>
-      <c r="G97" s="16" t="n"/>
-      <c r="H97" s="16">
+      <c r="G97" s="20" t="n"/>
+      <c r="H97" s="20">
         <f>IF(OR($B97="",$D97="",$E97=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B97)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B97&lt;&gt;"")*($G97&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I97" s="16">
+      <c r="I97" s="20">
         <f>IF($D97="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J97" s="17" t="n"/>
+      <c r="J97" s="21" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n">
+      <c r="A98" s="20" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="17" t="n"/>
-      <c r="C98" s="16" t="n"/>
-      <c r="D98" s="21" t="n"/>
-      <c r="E98" s="21" t="n"/>
-      <c r="F98" s="16">
+      <c r="B98" s="21" t="n"/>
+      <c r="C98" s="20" t="n"/>
+      <c r="D98" s="25" t="n"/>
+      <c r="E98" s="25" t="n"/>
+      <c r="F98" s="20">
         <f>IF(OR($D98="",$E98=""),"",$E98-$D98+1)</f>
         <v/>
       </c>
-      <c r="G98" s="16" t="n"/>
-      <c r="H98" s="16">
+      <c r="G98" s="20" t="n"/>
+      <c r="H98" s="20">
         <f>IF(OR($B98="",$D98="",$E98=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B98)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B98&lt;&gt;"")*($G98&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I98" s="16">
+      <c r="I98" s="20">
         <f>IF($D98="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J98" s="17" t="n"/>
+      <c r="J98" s="21" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n">
+      <c r="A99" s="20" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="17" t="n"/>
-      <c r="C99" s="16" t="n"/>
-      <c r="D99" s="21" t="n"/>
-      <c r="E99" s="21" t="n"/>
-      <c r="F99" s="16">
+      <c r="B99" s="21" t="n"/>
+      <c r="C99" s="20" t="n"/>
+      <c r="D99" s="25" t="n"/>
+      <c r="E99" s="25" t="n"/>
+      <c r="F99" s="20">
         <f>IF(OR($D99="",$E99=""),"",$E99-$D99+1)</f>
         <v/>
       </c>
-      <c r="G99" s="16" t="n"/>
-      <c r="H99" s="16">
+      <c r="G99" s="20" t="n"/>
+      <c r="H99" s="20">
         <f>IF(OR($B99="",$D99="",$E99=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B99)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B99&lt;&gt;"")*($G99&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I99" s="16">
+      <c r="I99" s="20">
         <f>IF($D99="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J99" s="17" t="n"/>
+      <c r="J99" s="21" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n">
+      <c r="A100" s="20" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="17" t="n"/>
-      <c r="C100" s="16" t="n"/>
-      <c r="D100" s="21" t="n"/>
-      <c r="E100" s="21" t="n"/>
-      <c r="F100" s="16">
+      <c r="B100" s="21" t="n"/>
+      <c r="C100" s="20" t="n"/>
+      <c r="D100" s="25" t="n"/>
+      <c r="E100" s="25" t="n"/>
+      <c r="F100" s="20">
         <f>IF(OR($D100="",$E100=""),"",$E100-$D100+1)</f>
         <v/>
       </c>
-      <c r="G100" s="16" t="n"/>
-      <c r="H100" s="16">
+      <c r="G100" s="20" t="n"/>
+      <c r="H100" s="20">
         <f>IF(OR($B100="",$D100="",$E100=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B100)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B100&lt;&gt;"")*($G100&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I100" s="16">
+      <c r="I100" s="20">
         <f>IF($D100="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J100" s="17" t="n"/>
+      <c r="J100" s="21" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n">
+      <c r="A101" s="20" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="17" t="n"/>
-      <c r="C101" s="16" t="n"/>
-      <c r="D101" s="21" t="n"/>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="16">
+      <c r="B101" s="21" t="n"/>
+      <c r="C101" s="20" t="n"/>
+      <c r="D101" s="25" t="n"/>
+      <c r="E101" s="25" t="n"/>
+      <c r="F101" s="20">
         <f>IF(OR($D101="",$E101=""),"",$E101-$D101+1)</f>
         <v/>
       </c>
-      <c r="G101" s="16" t="n"/>
-      <c r="H101" s="16">
+      <c r="G101" s="20" t="n"/>
+      <c r="H101" s="20">
         <f>IF(OR($B101="",$D101="",$E101=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B101)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B101&lt;&gt;"")*($G101&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I101" s="16">
+      <c r="I101" s="20">
         <f>IF($D101="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J101" s="17" t="n"/>
+      <c r="J101" s="21" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n">
+      <c r="A102" s="20" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="17" t="n"/>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="21" t="n"/>
-      <c r="E102" s="21" t="n"/>
-      <c r="F102" s="16">
+      <c r="B102" s="21" t="n"/>
+      <c r="C102" s="20" t="n"/>
+      <c r="D102" s="25" t="n"/>
+      <c r="E102" s="25" t="n"/>
+      <c r="F102" s="20">
         <f>IF(OR($D102="",$E102=""),"",$E102-$D102+1)</f>
         <v/>
       </c>
-      <c r="G102" s="16" t="n"/>
-      <c r="H102" s="16">
+      <c r="G102" s="20" t="n"/>
+      <c r="H102" s="20">
         <f>IF(OR($B102="",$D102="",$E102=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B102)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B102&lt;&gt;"")*($G102&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I102" s="16">
+      <c r="I102" s="20">
         <f>IF($D102="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J102" s="17" t="n"/>
+      <c r="J102" s="21" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n">
+      <c r="A103" s="20" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="17" t="n"/>
-      <c r="C103" s="16" t="n"/>
-      <c r="D103" s="21" t="n"/>
-      <c r="E103" s="21" t="n"/>
-      <c r="F103" s="16">
+      <c r="B103" s="21" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="25" t="n"/>
+      <c r="E103" s="25" t="n"/>
+      <c r="F103" s="20">
         <f>IF(OR($D103="",$E103=""),"",$E103-$D103+1)</f>
         <v/>
       </c>
-      <c r="G103" s="16" t="n"/>
-      <c r="H103" s="16">
+      <c r="G103" s="20" t="n"/>
+      <c r="H103" s="20">
         <f>IF(OR($B103="",$D103="",$E103=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B103)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B103&lt;&gt;"")*($G103&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I103" s="16">
+      <c r="I103" s="20">
         <f>IF($D103="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J103" s="17" t="n"/>
+      <c r="J103" s="21" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n">
+      <c r="A104" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="17" t="n"/>
-      <c r="C104" s="16" t="n"/>
-      <c r="D104" s="21" t="n"/>
-      <c r="E104" s="21" t="n"/>
-      <c r="F104" s="16">
+      <c r="B104" s="21" t="n"/>
+      <c r="C104" s="20" t="n"/>
+      <c r="D104" s="25" t="n"/>
+      <c r="E104" s="25" t="n"/>
+      <c r="F104" s="20">
         <f>IF(OR($D104="",$E104=""),"",$E104-$D104+1)</f>
         <v/>
       </c>
-      <c r="G104" s="16" t="n"/>
-      <c r="H104" s="16">
+      <c r="G104" s="20" t="n"/>
+      <c r="H104" s="20">
         <f>IF(OR($B104="",$D104="",$E104=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B104)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B104&lt;&gt;"")*($G104&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
       </c>
-      <c r="I104" s="16">
+      <c r="I104" s="20">
         <f>IF($D104="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
         <v/>
       </c>
-      <c r="J104" s="17" t="n"/>
+      <c r="J104" s="21" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H5:H104">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"⚠ تعارض"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
       <formula>"✓ سليم"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I104">
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="5">
       <formula>LEFT($I5)="⚠"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C104">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="6">
       <formula>"سنوية"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="7">
       <formula>"عارض"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="8">
       <formula>"دورية"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="9">
       <formula>"مرضية"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="10">
       <formula>"مرافق مريض"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="11">
       <formula>"أخرى"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3685,7 +3854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH23"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3725,1884 +3894,2297 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>جدول الورديات — 6 عمل / 4 راحة — الدوام 2:00 عصراً</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>جدول الورديات — 6 عمل / 4 راحة — صباح (6ص-1م) / عصر (1م-9م) / ليل (9م-6ص)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>التاريخ ←</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>الثلاثاء</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
         <is>
           <t>الأربعاء</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>الخميس</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>الجمعة</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="27" t="inlineStr">
         <is>
           <t>السبت</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="I2" s="27" t="inlineStr">
         <is>
           <t>الأحد</t>
         </is>
       </c>
-      <c r="J2" s="23" t="inlineStr">
+      <c r="J2" s="27" t="inlineStr">
         <is>
           <t>الإثنين</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="K2" s="27" t="inlineStr">
         <is>
           <t>الثلاثاء</t>
         </is>
       </c>
-      <c r="L2" s="23" t="inlineStr">
+      <c r="L2" s="27" t="inlineStr">
         <is>
           <t>الأربعاء</t>
         </is>
       </c>
-      <c r="M2" s="23" t="inlineStr">
+      <c r="M2" s="27" t="inlineStr">
         <is>
           <t>الخميس</t>
         </is>
       </c>
-      <c r="N2" s="23" t="inlineStr">
+      <c r="N2" s="27" t="inlineStr">
         <is>
           <t>الجمعة</t>
         </is>
       </c>
-      <c r="O2" s="23" t="inlineStr">
+      <c r="O2" s="27" t="inlineStr">
         <is>
           <t>السبت</t>
         </is>
       </c>
-      <c r="P2" s="23" t="inlineStr">
+      <c r="P2" s="27" t="inlineStr">
         <is>
           <t>الأحد</t>
         </is>
       </c>
-      <c r="Q2" s="23" t="inlineStr">
+      <c r="Q2" s="27" t="inlineStr">
         <is>
           <t>الإثنين</t>
         </is>
       </c>
-      <c r="R2" s="23" t="inlineStr">
+      <c r="R2" s="27" t="inlineStr">
         <is>
           <t>الثلاثاء</t>
         </is>
       </c>
-      <c r="S2" s="23" t="inlineStr">
+      <c r="S2" s="27" t="inlineStr">
         <is>
           <t>الأربعاء</t>
         </is>
       </c>
-      <c r="T2" s="23" t="inlineStr">
+      <c r="T2" s="27" t="inlineStr">
         <is>
           <t>الخميس</t>
         </is>
       </c>
-      <c r="U2" s="23" t="inlineStr">
+      <c r="U2" s="27" t="inlineStr">
         <is>
           <t>الجمعة</t>
         </is>
       </c>
-      <c r="V2" s="23" t="inlineStr">
+      <c r="V2" s="27" t="inlineStr">
         <is>
           <t>السبت</t>
         </is>
       </c>
-      <c r="W2" s="23" t="inlineStr">
+      <c r="W2" s="27" t="inlineStr">
         <is>
           <t>الأحد</t>
         </is>
       </c>
-      <c r="X2" s="23" t="inlineStr">
+      <c r="X2" s="27" t="inlineStr">
         <is>
           <t>الإثنين</t>
         </is>
       </c>
-      <c r="Y2" s="23" t="inlineStr">
+      <c r="Y2" s="27" t="inlineStr">
         <is>
           <t>الثلاثاء</t>
         </is>
       </c>
-      <c r="Z2" s="23" t="inlineStr">
+      <c r="Z2" s="27" t="inlineStr">
         <is>
           <t>الأربعاء</t>
         </is>
       </c>
-      <c r="AA2" s="23" t="inlineStr">
+      <c r="AA2" s="27" t="inlineStr">
         <is>
           <t>الخميس</t>
         </is>
       </c>
-      <c r="AB2" s="23" t="inlineStr">
+      <c r="AB2" s="27" t="inlineStr">
         <is>
           <t>الجمعة</t>
         </is>
       </c>
-      <c r="AC2" s="23" t="inlineStr">
+      <c r="AC2" s="27" t="inlineStr">
         <is>
           <t>السبت</t>
         </is>
       </c>
-      <c r="AD2" s="23" t="inlineStr">
+      <c r="AD2" s="27" t="inlineStr">
         <is>
           <t>الأحد</t>
         </is>
       </c>
-      <c r="AE2" s="23" t="inlineStr">
+      <c r="AE2" s="27" t="inlineStr">
         <is>
           <t>الإثنين</t>
         </is>
       </c>
-      <c r="AF2" s="23" t="inlineStr">
+      <c r="AF2" s="27" t="inlineStr">
         <is>
           <t>الثلاثاء</t>
         </is>
       </c>
-      <c r="AG2" s="23" t="inlineStr">
+      <c r="AG2" s="27" t="inlineStr">
         <is>
           <t>الأربعاء</t>
         </is>
       </c>
-      <c r="AH2" s="23" t="inlineStr">
+      <c r="AH2" s="27" t="inlineStr">
         <is>
           <t>الخميس</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>الرقم الوظيفي</t>
         </is>
       </c>
-      <c r="D3" s="24" t="n">
+      <c r="D3" s="28" t="n">
         <v>46189</v>
       </c>
-      <c r="E3" s="24" t="n">
+      <c r="E3" s="28" t="n">
         <v>46190</v>
       </c>
-      <c r="F3" s="24" t="n">
+      <c r="F3" s="28" t="n">
         <v>46191</v>
       </c>
-      <c r="G3" s="25" t="n">
+      <c r="G3" s="29" t="n">
         <v>46192</v>
       </c>
-      <c r="H3" s="24" t="n">
+      <c r="H3" s="28" t="n">
         <v>46193</v>
       </c>
-      <c r="I3" s="24" t="n">
+      <c r="I3" s="28" t="n">
         <v>46194</v>
       </c>
-      <c r="J3" s="24" t="n">
+      <c r="J3" s="28" t="n">
         <v>46195</v>
       </c>
-      <c r="K3" s="24" t="n">
+      <c r="K3" s="28" t="n">
         <v>46196</v>
       </c>
-      <c r="L3" s="24" t="n">
+      <c r="L3" s="28" t="n">
         <v>46197</v>
       </c>
-      <c r="M3" s="24" t="n">
+      <c r="M3" s="28" t="n">
         <v>46198</v>
       </c>
-      <c r="N3" s="25" t="n">
+      <c r="N3" s="29" t="n">
         <v>46199</v>
       </c>
-      <c r="O3" s="24" t="n">
+      <c r="O3" s="28" t="n">
         <v>46200</v>
       </c>
-      <c r="P3" s="24" t="n">
+      <c r="P3" s="28" t="n">
         <v>46201</v>
       </c>
-      <c r="Q3" s="24" t="n">
+      <c r="Q3" s="28" t="n">
         <v>46202</v>
       </c>
-      <c r="R3" s="24" t="n">
+      <c r="R3" s="28" t="n">
         <v>46203</v>
       </c>
-      <c r="S3" s="24" t="n">
+      <c r="S3" s="28" t="n">
         <v>46204</v>
       </c>
-      <c r="T3" s="24" t="n">
+      <c r="T3" s="28" t="n">
         <v>46205</v>
       </c>
-      <c r="U3" s="25" t="n">
+      <c r="U3" s="29" t="n">
         <v>46206</v>
       </c>
-      <c r="V3" s="24" t="n">
+      <c r="V3" s="28" t="n">
         <v>46207</v>
       </c>
-      <c r="W3" s="24" t="n">
+      <c r="W3" s="28" t="n">
         <v>46208</v>
       </c>
-      <c r="X3" s="24" t="n">
+      <c r="X3" s="28" t="n">
         <v>46209</v>
       </c>
-      <c r="Y3" s="24" t="n">
+      <c r="Y3" s="28" t="n">
         <v>46210</v>
       </c>
-      <c r="Z3" s="24" t="n">
+      <c r="Z3" s="28" t="n">
         <v>46211</v>
       </c>
-      <c r="AA3" s="24" t="n">
+      <c r="AA3" s="28" t="n">
         <v>46212</v>
       </c>
-      <c r="AB3" s="25" t="n">
+      <c r="AB3" s="29" t="n">
         <v>46213</v>
       </c>
-      <c r="AC3" s="24" t="n">
+      <c r="AC3" s="28" t="n">
         <v>46214</v>
       </c>
-      <c r="AD3" s="24" t="n">
+      <c r="AD3" s="28" t="n">
         <v>46215</v>
       </c>
-      <c r="AE3" s="24" t="n">
+      <c r="AE3" s="28" t="n">
         <v>46216</v>
       </c>
-      <c r="AF3" s="24" t="n">
+      <c r="AF3" s="28" t="n">
         <v>46217</v>
       </c>
-      <c r="AG3" s="24" t="n">
+      <c r="AG3" s="28" t="n">
         <v>46218</v>
       </c>
-      <c r="AH3" s="24" t="n">
+      <c r="AH3" s="28" t="n">
         <v>46219</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="21">
         <f>'الموظفون'!B2</f>
         <v/>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="20">
         <f>'الموظفون'!C2</f>
         <v/>
       </c>
-      <c r="D4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$2,"",IF(MOD(D$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$2,"",IF(MOD(E$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$2,"",IF(MOD(F$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$2,"",IF(MOD(G$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$2,"",IF(MOD(H$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$2,"",IF(MOD(I$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$2,"",IF(MOD(J$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$2,"",IF(MOD(K$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$2,"",IF(MOD(L$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$2,"",IF(MOD(M$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$2,"",IF(MOD(N$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$2,"",IF(MOD(O$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$2,"",IF(MOD(P$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$2,"",IF(MOD(Q$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$2,"",IF(MOD(R$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$2,"",IF(MOD(S$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$2,"",IF(MOD(T$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$2,"",IF(MOD(U$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$2,"",IF(MOD(V$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$2,"",IF(MOD(W$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$2,"",IF(MOD(X$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$2,"",IF(MOD(Y$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$2,"",IF(MOD(Z$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$2,"",IF(MOD(AA$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$2,"",IF(MOD(AB$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$2,"",IF(MOD(AC$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$2,"",IF(MOD(AD$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$2,"",IF(MOD(AE$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$2,"",IF(MOD(AF$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$2,"",IF(MOD(AG$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH4" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$2,"",IF(MOD(AH$3-'الموظفون'!$D$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$2,"",IF(MOD(D$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$2,"",IF(MOD(E$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$2,"",IF(MOD(F$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$2,"",IF(MOD(G$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$2,"",IF(MOD(H$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$2,"",IF(MOD(I$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$2,"",IF(MOD(J$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$2,"",IF(MOD(K$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$2,"",IF(MOD(L$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$2,"",IF(MOD(M$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$2,"",IF(MOD(N$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$2,"",IF(MOD(O$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$2,"",IF(MOD(P$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$2,"",IF(MOD(Q$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$2,"",IF(MOD(R$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$2,"",IF(MOD(S$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$2,"",IF(MOD(T$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$2,"",IF(MOD(U$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$2,"",IF(MOD(V$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$2,"",IF(MOD(W$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$2,"",IF(MOD(X$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$2,"",IF(MOD(Y$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$2,"",IF(MOD(Z$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$2,"",IF(MOD(AA$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$2,"",IF(MOD(AB$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$2,"",IF(MOD(AC$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$2,"",IF(MOD(AD$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$2,"",IF(MOD(AE$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$2,"",IF(MOD(AF$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$2,"",IF(MOD(AG$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$2,"",IF(MOD(AH$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="21">
         <f>'الموظفون'!B3</f>
         <v/>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="20">
         <f>'الموظفون'!C3</f>
         <v/>
       </c>
-      <c r="D5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$3,"",IF(MOD(D$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$3,"",IF(MOD(E$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$3,"",IF(MOD(F$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$3,"",IF(MOD(G$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$3,"",IF(MOD(H$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$3,"",IF(MOD(I$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$3,"",IF(MOD(J$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$3,"",IF(MOD(K$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$3,"",IF(MOD(L$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$3,"",IF(MOD(M$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$3,"",IF(MOD(N$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$3,"",IF(MOD(O$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$3,"",IF(MOD(P$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$3,"",IF(MOD(Q$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$3,"",IF(MOD(R$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$3,"",IF(MOD(S$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$3,"",IF(MOD(T$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$3,"",IF(MOD(U$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$3,"",IF(MOD(V$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$3,"",IF(MOD(W$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$3,"",IF(MOD(X$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$3,"",IF(MOD(Y$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$3,"",IF(MOD(Z$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$3,"",IF(MOD(AA$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$3,"",IF(MOD(AB$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$3,"",IF(MOD(AC$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$3,"",IF(MOD(AD$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$3,"",IF(MOD(AE$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$3,"",IF(MOD(AF$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$3,"",IF(MOD(AG$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH5" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$3,"",IF(MOD(AH$3-'الموظفون'!$D$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$3,"",IF(MOD(D$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$3,"",IF(MOD(E$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$3,"",IF(MOD(F$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$3,"",IF(MOD(G$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$3,"",IF(MOD(H$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$3,"",IF(MOD(I$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$3,"",IF(MOD(J$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$3,"",IF(MOD(K$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$3,"",IF(MOD(L$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$3,"",IF(MOD(M$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$3,"",IF(MOD(N$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$3,"",IF(MOD(O$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$3,"",IF(MOD(P$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$3,"",IF(MOD(Q$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$3,"",IF(MOD(R$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$3,"",IF(MOD(S$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$3,"",IF(MOD(T$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$3,"",IF(MOD(U$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$3,"",IF(MOD(V$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$3,"",IF(MOD(W$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$3,"",IF(MOD(X$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$3,"",IF(MOD(Y$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$3,"",IF(MOD(Z$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$3,"",IF(MOD(AA$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$3,"",IF(MOD(AB$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$3,"",IF(MOD(AC$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$3,"",IF(MOD(AD$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$3,"",IF(MOD(AE$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$3,"",IF(MOD(AF$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$3,"",IF(MOD(AG$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$3,"",IF(MOD(AH$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="21">
         <f>'الموظفون'!B4</f>
         <v/>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="20">
         <f>'الموظفون'!C4</f>
         <v/>
       </c>
-      <c r="D6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$4,"",IF(MOD(D$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$4,"",IF(MOD(E$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$4,"",IF(MOD(F$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$4,"",IF(MOD(G$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$4,"",IF(MOD(H$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$4,"",IF(MOD(I$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$4,"",IF(MOD(J$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$4,"",IF(MOD(K$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$4,"",IF(MOD(L$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$4,"",IF(MOD(M$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$4,"",IF(MOD(N$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$4,"",IF(MOD(O$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$4,"",IF(MOD(P$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$4,"",IF(MOD(Q$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$4,"",IF(MOD(R$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$4,"",IF(MOD(S$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$4,"",IF(MOD(T$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$4,"",IF(MOD(U$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$4,"",IF(MOD(V$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$4,"",IF(MOD(W$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$4,"",IF(MOD(X$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$4,"",IF(MOD(Y$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$4,"",IF(MOD(Z$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$4,"",IF(MOD(AA$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$4,"",IF(MOD(AB$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$4,"",IF(MOD(AC$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$4,"",IF(MOD(AD$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$4,"",IF(MOD(AE$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$4,"",IF(MOD(AF$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$4,"",IF(MOD(AG$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH6" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$4,"",IF(MOD(AH$3-'الموظفون'!$D$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$4,"",IF(MOD(D$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$4,"",IF(MOD(E$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$4,"",IF(MOD(F$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$4,"",IF(MOD(G$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$4,"",IF(MOD(H$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$4,"",IF(MOD(I$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$4,"",IF(MOD(J$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$4,"",IF(MOD(K$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$4,"",IF(MOD(L$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$4,"",IF(MOD(M$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$4,"",IF(MOD(N$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$4,"",IF(MOD(O$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$4,"",IF(MOD(P$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$4,"",IF(MOD(Q$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$4,"",IF(MOD(R$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$4,"",IF(MOD(S$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$4,"",IF(MOD(T$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$4,"",IF(MOD(U$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$4,"",IF(MOD(V$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$4,"",IF(MOD(W$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$4,"",IF(MOD(X$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$4,"",IF(MOD(Y$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$4,"",IF(MOD(Z$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$4,"",IF(MOD(AA$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$4,"",IF(MOD(AB$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$4,"",IF(MOD(AC$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$4,"",IF(MOD(AD$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$4,"",IF(MOD(AE$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$4,"",IF(MOD(AF$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$4,"",IF(MOD(AG$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$4,"",IF(MOD(AH$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="21">
         <f>'الموظفون'!B5</f>
         <v/>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="20">
         <f>'الموظفون'!C5</f>
         <v/>
       </c>
-      <c r="D7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$5,"",IF(MOD(D$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$5,"",IF(MOD(E$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$5,"",IF(MOD(F$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$5,"",IF(MOD(G$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$5,"",IF(MOD(H$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$5,"",IF(MOD(I$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$5,"",IF(MOD(J$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$5,"",IF(MOD(K$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$5,"",IF(MOD(L$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$5,"",IF(MOD(M$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$5,"",IF(MOD(N$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$5,"",IF(MOD(O$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$5,"",IF(MOD(P$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$5,"",IF(MOD(Q$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$5,"",IF(MOD(R$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$5,"",IF(MOD(S$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$5,"",IF(MOD(T$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$5,"",IF(MOD(U$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$5,"",IF(MOD(V$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$5,"",IF(MOD(W$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$5,"",IF(MOD(X$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$5,"",IF(MOD(Y$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$5,"",IF(MOD(Z$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$5,"",IF(MOD(AA$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$5,"",IF(MOD(AB$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$5,"",IF(MOD(AC$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$5,"",IF(MOD(AD$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$5,"",IF(MOD(AE$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$5,"",IF(MOD(AF$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$5,"",IF(MOD(AG$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH7" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$5,"",IF(MOD(AH$3-'الموظفون'!$D$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$5,"",IF(MOD(D$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$5,"",IF(MOD(E$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$5,"",IF(MOD(F$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$5,"",IF(MOD(G$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$5,"",IF(MOD(H$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$5,"",IF(MOD(I$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$5,"",IF(MOD(J$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$5,"",IF(MOD(K$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$5,"",IF(MOD(L$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$5,"",IF(MOD(M$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$5,"",IF(MOD(N$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$5,"",IF(MOD(O$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$5,"",IF(MOD(P$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$5,"",IF(MOD(Q$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$5,"",IF(MOD(R$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$5,"",IF(MOD(S$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$5,"",IF(MOD(T$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$5,"",IF(MOD(U$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$5,"",IF(MOD(V$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$5,"",IF(MOD(W$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$5,"",IF(MOD(X$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$5,"",IF(MOD(Y$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$5,"",IF(MOD(Z$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$5,"",IF(MOD(AA$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$5,"",IF(MOD(AB$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$5,"",IF(MOD(AC$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$5,"",IF(MOD(AD$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$5,"",IF(MOD(AE$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$5,"",IF(MOD(AF$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$5,"",IF(MOD(AG$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$5,"",IF(MOD(AH$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="21">
         <f>'الموظفون'!B6</f>
         <v/>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="20">
         <f>'الموظفون'!C6</f>
         <v/>
       </c>
-      <c r="D8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$6,"",IF(MOD(D$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$6,"",IF(MOD(E$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$6,"",IF(MOD(F$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$6,"",IF(MOD(G$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$6,"",IF(MOD(H$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$6,"",IF(MOD(I$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$6,"",IF(MOD(J$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$6,"",IF(MOD(K$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$6,"",IF(MOD(L$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$6,"",IF(MOD(M$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$6,"",IF(MOD(N$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$6,"",IF(MOD(O$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$6,"",IF(MOD(P$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$6,"",IF(MOD(Q$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$6,"",IF(MOD(R$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$6,"",IF(MOD(S$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$6,"",IF(MOD(T$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$6,"",IF(MOD(U$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$6,"",IF(MOD(V$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$6,"",IF(MOD(W$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$6,"",IF(MOD(X$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$6,"",IF(MOD(Y$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$6,"",IF(MOD(Z$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$6,"",IF(MOD(AA$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$6,"",IF(MOD(AB$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$6,"",IF(MOD(AC$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$6,"",IF(MOD(AD$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$6,"",IF(MOD(AE$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$6,"",IF(MOD(AF$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$6,"",IF(MOD(AG$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH8" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$6,"",IF(MOD(AH$3-'الموظفون'!$D$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$6,"",IF(MOD(D$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$6,"",IF(MOD(E$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$6,"",IF(MOD(F$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$6,"",IF(MOD(G$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$6,"",IF(MOD(H$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$6,"",IF(MOD(I$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$6,"",IF(MOD(J$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$6,"",IF(MOD(K$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$6,"",IF(MOD(L$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$6,"",IF(MOD(M$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$6,"",IF(MOD(N$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$6,"",IF(MOD(O$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$6,"",IF(MOD(P$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$6,"",IF(MOD(Q$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$6,"",IF(MOD(R$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$6,"",IF(MOD(S$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$6,"",IF(MOD(T$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$6,"",IF(MOD(U$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$6,"",IF(MOD(V$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$6,"",IF(MOD(W$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$6,"",IF(MOD(X$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$6,"",IF(MOD(Y$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$6,"",IF(MOD(Z$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$6,"",IF(MOD(AA$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$6,"",IF(MOD(AB$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$6,"",IF(MOD(AC$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$6,"",IF(MOD(AD$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$6,"",IF(MOD(AE$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$6,"",IF(MOD(AF$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$6,"",IF(MOD(AG$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$6,"",IF(MOD(AH$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="21">
         <f>'الموظفون'!B7</f>
         <v/>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="20">
         <f>'الموظفون'!C7</f>
         <v/>
       </c>
-      <c r="D9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$7,"",IF(MOD(D$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$7,"",IF(MOD(E$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$7,"",IF(MOD(F$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$7,"",IF(MOD(G$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$7,"",IF(MOD(H$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$7,"",IF(MOD(I$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$7,"",IF(MOD(J$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$7,"",IF(MOD(K$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$7,"",IF(MOD(L$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$7,"",IF(MOD(M$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$7,"",IF(MOD(N$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$7,"",IF(MOD(O$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$7,"",IF(MOD(P$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$7,"",IF(MOD(Q$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$7,"",IF(MOD(R$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$7,"",IF(MOD(S$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$7,"",IF(MOD(T$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$7,"",IF(MOD(U$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$7,"",IF(MOD(V$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$7,"",IF(MOD(W$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$7,"",IF(MOD(X$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$7,"",IF(MOD(Y$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$7,"",IF(MOD(Z$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$7,"",IF(MOD(AA$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$7,"",IF(MOD(AB$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$7,"",IF(MOD(AC$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$7,"",IF(MOD(AD$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$7,"",IF(MOD(AE$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$7,"",IF(MOD(AF$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$7,"",IF(MOD(AG$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH9" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$7,"",IF(MOD(AH$3-'الموظفون'!$D$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$7,"",IF(MOD(D$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$7,"",IF(MOD(E$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$7,"",IF(MOD(F$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$7,"",IF(MOD(G$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$7,"",IF(MOD(H$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$7,"",IF(MOD(I$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$7,"",IF(MOD(J$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$7,"",IF(MOD(K$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$7,"",IF(MOD(L$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$7,"",IF(MOD(M$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$7,"",IF(MOD(N$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$7,"",IF(MOD(O$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$7,"",IF(MOD(P$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$7,"",IF(MOD(Q$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$7,"",IF(MOD(R$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$7,"",IF(MOD(S$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$7,"",IF(MOD(T$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$7,"",IF(MOD(U$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$7,"",IF(MOD(V$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$7,"",IF(MOD(W$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$7,"",IF(MOD(X$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$7,"",IF(MOD(Y$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$7,"",IF(MOD(Z$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$7,"",IF(MOD(AA$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$7,"",IF(MOD(AB$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$7,"",IF(MOD(AC$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$7,"",IF(MOD(AD$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$7,"",IF(MOD(AE$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$7,"",IF(MOD(AF$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$7,"",IF(MOD(AG$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$7,"",IF(MOD(AH$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="21">
         <f>'الموظفون'!B8</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="20">
         <f>'الموظفون'!C8</f>
         <v/>
       </c>
-      <c r="D10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$8,"",IF(MOD(D$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$8,"",IF(MOD(E$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$8,"",IF(MOD(F$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$8,"",IF(MOD(G$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$8,"",IF(MOD(H$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$8,"",IF(MOD(I$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$8,"",IF(MOD(J$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$8,"",IF(MOD(K$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$8,"",IF(MOD(L$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$8,"",IF(MOD(M$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$8,"",IF(MOD(N$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$8,"",IF(MOD(O$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$8,"",IF(MOD(P$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$8,"",IF(MOD(Q$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$8,"",IF(MOD(R$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$8,"",IF(MOD(S$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$8,"",IF(MOD(T$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$8,"",IF(MOD(U$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$8,"",IF(MOD(V$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$8,"",IF(MOD(W$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$8,"",IF(MOD(X$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$8,"",IF(MOD(Y$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$8,"",IF(MOD(Z$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$8,"",IF(MOD(AA$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$8,"",IF(MOD(AB$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$8,"",IF(MOD(AC$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$8,"",IF(MOD(AD$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$8,"",IF(MOD(AE$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$8,"",IF(MOD(AF$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$8,"",IF(MOD(AG$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH10" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$8,"",IF(MOD(AH$3-'الموظفون'!$D$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$8,"",IF(MOD(D$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$8,"",IF(MOD(E$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$8,"",IF(MOD(F$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$8,"",IF(MOD(G$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$8,"",IF(MOD(H$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$8,"",IF(MOD(I$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$8,"",IF(MOD(J$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$8,"",IF(MOD(K$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$8,"",IF(MOD(L$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$8,"",IF(MOD(M$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$8,"",IF(MOD(N$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$8,"",IF(MOD(O$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$8,"",IF(MOD(P$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$8,"",IF(MOD(Q$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$8,"",IF(MOD(R$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$8,"",IF(MOD(S$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$8,"",IF(MOD(T$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$8,"",IF(MOD(U$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$8,"",IF(MOD(V$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$8,"",IF(MOD(W$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$8,"",IF(MOD(X$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$8,"",IF(MOD(Y$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$8,"",IF(MOD(Z$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$8,"",IF(MOD(AA$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$8,"",IF(MOD(AB$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$8,"",IF(MOD(AC$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$8,"",IF(MOD(AD$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$8,"",IF(MOD(AE$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$8,"",IF(MOD(AF$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$8,"",IF(MOD(AG$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$8,"",IF(MOD(AH$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="21">
         <f>'الموظفون'!B9</f>
         <v/>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="20">
         <f>'الموظفون'!C9</f>
         <v/>
       </c>
-      <c r="D11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$D$9,"",IF(MOD(D$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="E11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$D$9,"",IF(MOD(E$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="F11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$D$9,"",IF(MOD(F$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="G11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$D$9,"",IF(MOD(G$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="H11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$D$9,"",IF(MOD(H$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="I11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$D$9,"",IF(MOD(I$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="J11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$D$9,"",IF(MOD(J$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="K11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$D$9,"",IF(MOD(K$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="L11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$D$9,"",IF(MOD(L$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="M11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$D$9,"",IF(MOD(M$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="N11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$D$9,"",IF(MOD(N$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="O11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$D$9,"",IF(MOD(O$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="P11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$D$9,"",IF(MOD(P$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$D$9,"",IF(MOD(Q$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="R11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$D$9,"",IF(MOD(R$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="S11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$D$9,"",IF(MOD(S$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="T11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$D$9,"",IF(MOD(T$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="U11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$D$9,"",IF(MOD(U$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="V11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$D$9,"",IF(MOD(V$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="W11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$D$9,"",IF(MOD(W$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="X11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$D$9,"",IF(MOD(X$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Y11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$D$9,"",IF(MOD(Y$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="Z11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$D$9,"",IF(MOD(Z$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AA11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$D$9,"",IF(MOD(AA$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AB11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$D$9,"",IF(MOD(AB$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AC11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$D$9,"",IF(MOD(AC$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AD11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$D$9,"",IF(MOD(AD$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AE11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$D$9,"",IF(MOD(AE$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AF11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$D$9,"",IF(MOD(AF$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AG11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$D$9,"",IF(MOD(AG$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
-        <v/>
-      </c>
-      <c r="AH11" s="26">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$D$9,"",IF(MOD(AH$3-'الموظفون'!$D$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,"عمل","راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+      <c r="D11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$9,"",IF(MOD(D$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$9,"",IF(MOD(E$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$9,"",IF(MOD(F$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$9,"",IF(MOD(G$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$9,"",IF(MOD(H$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$9,"",IF(MOD(I$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$9,"",IF(MOD(J$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$9,"",IF(MOD(K$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$9,"",IF(MOD(L$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$9,"",IF(MOD(M$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$9,"",IF(MOD(N$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$9,"",IF(MOD(O$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$9,"",IF(MOD(P$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$9,"",IF(MOD(Q$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$9,"",IF(MOD(R$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$9,"",IF(MOD(S$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$9,"",IF(MOD(T$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$9,"",IF(MOD(U$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$9,"",IF(MOD(V$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$9,"",IF(MOD(W$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$9,"",IF(MOD(X$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$9,"",IF(MOD(Y$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$9,"",IF(MOD(Z$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$9,"",IF(MOD(AA$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$9,"",IF(MOD(AB$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$9,"",IF(MOD(AC$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$9,"",IF(MOD(AD$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$9,"",IF(MOD(AE$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$9,"",IF(MOD(AF$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$9,"",IF(MOD(AG$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$9,"",IF(MOD(AH$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>عدد العاملين (عمل)</t>
-        </is>
-      </c>
-      <c r="D12" s="28">
-        <f>COUNTIF(D4:D11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="E12" s="28">
-        <f>COUNTIF(E4:E11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>COUNTIF(F4:F11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>COUNTIF(G4:G11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="H12" s="28">
-        <f>COUNTIF(H4:H11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="I12" s="28">
-        <f>COUNTIF(I4:I11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="J12" s="28">
-        <f>COUNTIF(J4:J11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="K12" s="28">
-        <f>COUNTIF(K4:K11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="L12" s="28">
-        <f>COUNTIF(L4:L11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="M12" s="28">
-        <f>COUNTIF(M4:M11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="N12" s="28">
-        <f>COUNTIF(N4:N11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="O12" s="28">
-        <f>COUNTIF(O4:O11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="P12" s="28">
-        <f>COUNTIF(P4:P11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="28">
-        <f>COUNTIF(Q4:Q11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="R12" s="28">
-        <f>COUNTIF(R4:R11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="S12" s="28">
-        <f>COUNTIF(S4:S11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="T12" s="28">
-        <f>COUNTIF(T4:T11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="U12" s="28">
-        <f>COUNTIF(U4:U11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="V12" s="28">
-        <f>COUNTIF(V4:V11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="W12" s="28">
-        <f>COUNTIF(W4:W11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="X12" s="28">
-        <f>COUNTIF(X4:X11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="Y12" s="28">
-        <f>COUNTIF(Y4:Y11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="Z12" s="28">
-        <f>COUNTIF(Z4:Z11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AA12" s="28">
-        <f>COUNTIF(AA4:AA11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AB12" s="28">
-        <f>COUNTIF(AB4:AB11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AC12" s="28">
-        <f>COUNTIF(AC4:AC11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AD12" s="28">
-        <f>COUNTIF(AD4:AD11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AE12" s="28">
-        <f>COUNTIF(AE4:AE11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AF12" s="28">
-        <f>COUNTIF(AF4:AF11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AG12" s="28">
-        <f>COUNTIF(AG4:AG11,"عمل")</f>
-        <v/>
-      </c>
-      <c r="AH12" s="28">
-        <f>COUNTIF(AH4:AH11,"عمل")</f>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>صباح</t>
+        </is>
+      </c>
+      <c r="D12" s="32">
+        <f>COUNTIF(D4:D11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>COUNTIF(E4:E11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>COUNTIF(F4:F11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="G12" s="32">
+        <f>COUNTIF(G4:G11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="H12" s="32">
+        <f>COUNTIF(H4:H11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="I12" s="32">
+        <f>COUNTIF(I4:I11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="J12" s="32">
+        <f>COUNTIF(J4:J11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="K12" s="32">
+        <f>COUNTIF(K4:K11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="L12" s="32">
+        <f>COUNTIF(L4:L11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="M12" s="32">
+        <f>COUNTIF(M4:M11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="N12" s="32">
+        <f>COUNTIF(N4:N11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="O12" s="32">
+        <f>COUNTIF(O4:O11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="P12" s="32">
+        <f>COUNTIF(P4:P11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="32">
+        <f>COUNTIF(Q4:Q11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="R12" s="32">
+        <f>COUNTIF(R4:R11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="S12" s="32">
+        <f>COUNTIF(S4:S11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="T12" s="32">
+        <f>COUNTIF(T4:T11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="U12" s="32">
+        <f>COUNTIF(U4:U11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="V12" s="32">
+        <f>COUNTIF(V4:V11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="W12" s="32">
+        <f>COUNTIF(W4:W11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="X12" s="32">
+        <f>COUNTIF(X4:X11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="Y12" s="32">
+        <f>COUNTIF(Y4:Y11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="Z12" s="32">
+        <f>COUNTIF(Z4:Z11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AA12" s="32">
+        <f>COUNTIF(AA4:AA11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AB12" s="32">
+        <f>COUNTIF(AB4:AB11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AC12" s="32">
+        <f>COUNTIF(AC4:AC11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="32">
+        <f>COUNTIF(AD4:AD11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AE12" s="32">
+        <f>COUNTIF(AE4:AE11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AF12" s="32">
+        <f>COUNTIF(AF4:AF11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AG12" s="32">
+        <f>COUNTIF(AG4:AG11,"صباح")</f>
+        <v/>
+      </c>
+      <c r="AH12" s="32">
+        <f>COUNTIF(AH4:AH11,"صباح")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+      <c r="D13" s="32">
+        <f>COUNTIF(D4:D11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="E13" s="32">
+        <f>COUNTIF(E4:E11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="F13" s="32">
+        <f>COUNTIF(F4:F11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="G13" s="32">
+        <f>COUNTIF(G4:G11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="H13" s="32">
+        <f>COUNTIF(H4:H11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="I13" s="32">
+        <f>COUNTIF(I4:I11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="J13" s="32">
+        <f>COUNTIF(J4:J11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="K13" s="32">
+        <f>COUNTIF(K4:K11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="L13" s="32">
+        <f>COUNTIF(L4:L11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="M13" s="32">
+        <f>COUNTIF(M4:M11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="N13" s="32">
+        <f>COUNTIF(N4:N11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="O13" s="32">
+        <f>COUNTIF(O4:O11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="P13" s="32">
+        <f>COUNTIF(P4:P11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="32">
+        <f>COUNTIF(Q4:Q11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="R13" s="32">
+        <f>COUNTIF(R4:R11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="S13" s="32">
+        <f>COUNTIF(S4:S11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="T13" s="32">
+        <f>COUNTIF(T4:T11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="U13" s="32">
+        <f>COUNTIF(U4:U11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="V13" s="32">
+        <f>COUNTIF(V4:V11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="W13" s="32">
+        <f>COUNTIF(W4:W11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="X13" s="32">
+        <f>COUNTIF(X4:X11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="Y13" s="32">
+        <f>COUNTIF(Y4:Y11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="Z13" s="32">
+        <f>COUNTIF(Z4:Z11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AA13" s="32">
+        <f>COUNTIF(AA4:AA11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AB13" s="32">
+        <f>COUNTIF(AB4:AB11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AC13" s="32">
+        <f>COUNTIF(AC4:AC11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="32">
+        <f>COUNTIF(AD4:AD11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AE13" s="32">
+        <f>COUNTIF(AE4:AE11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AF13" s="32">
+        <f>COUNTIF(AF4:AF11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AG13" s="32">
+        <f>COUNTIF(AG4:AG11,"عصر")</f>
+        <v/>
+      </c>
+      <c r="AH13" s="32">
+        <f>COUNTIF(AH4:AH11,"عصر")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>ليل</t>
+        </is>
+      </c>
+      <c r="D14" s="32">
+        <f>COUNTIF(D4:D11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="E14" s="32">
+        <f>COUNTIF(E4:E11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="F14" s="32">
+        <f>COUNTIF(F4:F11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="G14" s="32">
+        <f>COUNTIF(G4:G11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="H14" s="32">
+        <f>COUNTIF(H4:H11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="I14" s="32">
+        <f>COUNTIF(I4:I11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="J14" s="32">
+        <f>COUNTIF(J4:J11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="K14" s="32">
+        <f>COUNTIF(K4:K11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="L14" s="32">
+        <f>COUNTIF(L4:L11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="M14" s="32">
+        <f>COUNTIF(M4:M11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="N14" s="32">
+        <f>COUNTIF(N4:N11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="O14" s="32">
+        <f>COUNTIF(O4:O11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="P14" s="32">
+        <f>COUNTIF(P4:P11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="32">
+        <f>COUNTIF(Q4:Q11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="R14" s="32">
+        <f>COUNTIF(R4:R11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="S14" s="32">
+        <f>COUNTIF(S4:S11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="T14" s="32">
+        <f>COUNTIF(T4:T11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="U14" s="32">
+        <f>COUNTIF(U4:U11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="V14" s="32">
+        <f>COUNTIF(V4:V11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="W14" s="32">
+        <f>COUNTIF(W4:W11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="X14" s="32">
+        <f>COUNTIF(X4:X11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="Y14" s="32">
+        <f>COUNTIF(Y4:Y11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="Z14" s="32">
+        <f>COUNTIF(Z4:Z11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AA14" s="32">
+        <f>COUNTIF(AA4:AA11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AB14" s="32">
+        <f>COUNTIF(AB4:AB11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AC14" s="32">
+        <f>COUNTIF(AC4:AC11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="32">
+        <f>COUNTIF(AD4:AD11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AE14" s="32">
+        <f>COUNTIF(AE4:AE11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AF14" s="32">
+        <f>COUNTIF(AF4:AF11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AG14" s="32">
+        <f>COUNTIF(AG4:AG11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AH14" s="32">
+        <f>COUNTIF(AH4:AH11,"ليل")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>إجمالي العاملين</t>
+        </is>
+      </c>
+      <c r="D15" s="32">
+        <f>COUNTIF(D4:D11,"صباح")+COUNTIF(D4:D11,"عصر")+COUNTIF(D4:D11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>COUNTIF(E4:E11,"صباح")+COUNTIF(E4:E11,"عصر")+COUNTIF(E4:E11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
+        <f>COUNTIF(F4:F11,"صباح")+COUNTIF(F4:F11,"عصر")+COUNTIF(F4:F11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="G15" s="32">
+        <f>COUNTIF(G4:G11,"صباح")+COUNTIF(G4:G11,"عصر")+COUNTIF(G4:G11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="H15" s="32">
+        <f>COUNTIF(H4:H11,"صباح")+COUNTIF(H4:H11,"عصر")+COUNTIF(H4:H11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="I15" s="32">
+        <f>COUNTIF(I4:I11,"صباح")+COUNTIF(I4:I11,"عصر")+COUNTIF(I4:I11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="J15" s="32">
+        <f>COUNTIF(J4:J11,"صباح")+COUNTIF(J4:J11,"عصر")+COUNTIF(J4:J11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="K15" s="32">
+        <f>COUNTIF(K4:K11,"صباح")+COUNTIF(K4:K11,"عصر")+COUNTIF(K4:K11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="L15" s="32">
+        <f>COUNTIF(L4:L11,"صباح")+COUNTIF(L4:L11,"عصر")+COUNTIF(L4:L11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="M15" s="32">
+        <f>COUNTIF(M4:M11,"صباح")+COUNTIF(M4:M11,"عصر")+COUNTIF(M4:M11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="N15" s="32">
+        <f>COUNTIF(N4:N11,"صباح")+COUNTIF(N4:N11,"عصر")+COUNTIF(N4:N11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="O15" s="32">
+        <f>COUNTIF(O4:O11,"صباح")+COUNTIF(O4:O11,"عصر")+COUNTIF(O4:O11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="P15" s="32">
+        <f>COUNTIF(P4:P11,"صباح")+COUNTIF(P4:P11,"عصر")+COUNTIF(P4:P11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="32">
+        <f>COUNTIF(Q4:Q11,"صباح")+COUNTIF(Q4:Q11,"عصر")+COUNTIF(Q4:Q11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="R15" s="32">
+        <f>COUNTIF(R4:R11,"صباح")+COUNTIF(R4:R11,"عصر")+COUNTIF(R4:R11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="S15" s="32">
+        <f>COUNTIF(S4:S11,"صباح")+COUNTIF(S4:S11,"عصر")+COUNTIF(S4:S11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="T15" s="32">
+        <f>COUNTIF(T4:T11,"صباح")+COUNTIF(T4:T11,"عصر")+COUNTIF(T4:T11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="U15" s="32">
+        <f>COUNTIF(U4:U11,"صباح")+COUNTIF(U4:U11,"عصر")+COUNTIF(U4:U11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="V15" s="32">
+        <f>COUNTIF(V4:V11,"صباح")+COUNTIF(V4:V11,"عصر")+COUNTIF(V4:V11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="W15" s="32">
+        <f>COUNTIF(W4:W11,"صباح")+COUNTIF(W4:W11,"عصر")+COUNTIF(W4:W11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="X15" s="32">
+        <f>COUNTIF(X4:X11,"صباح")+COUNTIF(X4:X11,"عصر")+COUNTIF(X4:X11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="Y15" s="32">
+        <f>COUNTIF(Y4:Y11,"صباح")+COUNTIF(Y4:Y11,"عصر")+COUNTIF(Y4:Y11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="Z15" s="32">
+        <f>COUNTIF(Z4:Z11,"صباح")+COUNTIF(Z4:Z11,"عصر")+COUNTIF(Z4:Z11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AA15" s="32">
+        <f>COUNTIF(AA4:AA11,"صباح")+COUNTIF(AA4:AA11,"عصر")+COUNTIF(AA4:AA11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AB15" s="32">
+        <f>COUNTIF(AB4:AB11,"صباح")+COUNTIF(AB4:AB11,"عصر")+COUNTIF(AB4:AB11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AC15" s="32">
+        <f>COUNTIF(AC4:AC11,"صباح")+COUNTIF(AC4:AC11,"عصر")+COUNTIF(AC4:AC11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="32">
+        <f>COUNTIF(AD4:AD11,"صباح")+COUNTIF(AD4:AD11,"عصر")+COUNTIF(AD4:AD11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AE15" s="32">
+        <f>COUNTIF(AE4:AE11,"صباح")+COUNTIF(AE4:AE11,"عصر")+COUNTIF(AE4:AE11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AF15" s="32">
+        <f>COUNTIF(AF4:AF11,"صباح")+COUNTIF(AF4:AF11,"عصر")+COUNTIF(AF4:AF11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AG15" s="32">
+        <f>COUNTIF(AG4:AG11,"صباح")+COUNTIF(AG4:AG11,"عصر")+COUNTIF(AG4:AG11,"ليل")</f>
+        <v/>
+      </c>
+      <c r="AH15" s="32">
+        <f>COUNTIF(AH4:AH11,"صباح")+COUNTIF(AH4:AH11,"عصر")+COUNTIF(AH4:AH11,"ليل")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>عدد المُجازين</t>
         </is>
       </c>
-      <c r="D13" s="28">
-        <f>SUMPRODUCT((D4:D11&lt;&gt;"")*(D4:D11&lt;&gt;"عمل")*(D4:D11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="E13" s="28">
-        <f>SUMPRODUCT((E4:E11&lt;&gt;"")*(E4:E11&lt;&gt;"عمل")*(E4:E11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="F13" s="28">
-        <f>SUMPRODUCT((F4:F11&lt;&gt;"")*(F4:F11&lt;&gt;"عمل")*(F4:F11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="28">
-        <f>SUMPRODUCT((G4:G11&lt;&gt;"")*(G4:G11&lt;&gt;"عمل")*(G4:G11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="28">
-        <f>SUMPRODUCT((H4:H11&lt;&gt;"")*(H4:H11&lt;&gt;"عمل")*(H4:H11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="I13" s="28">
-        <f>SUMPRODUCT((I4:I11&lt;&gt;"")*(I4:I11&lt;&gt;"عمل")*(I4:I11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="J13" s="28">
-        <f>SUMPRODUCT((J4:J11&lt;&gt;"")*(J4:J11&lt;&gt;"عمل")*(J4:J11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="K13" s="28">
-        <f>SUMPRODUCT((K4:K11&lt;&gt;"")*(K4:K11&lt;&gt;"عمل")*(K4:K11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="L13" s="28">
-        <f>SUMPRODUCT((L4:L11&lt;&gt;"")*(L4:L11&lt;&gt;"عمل")*(L4:L11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="M13" s="28">
-        <f>SUMPRODUCT((M4:M11&lt;&gt;"")*(M4:M11&lt;&gt;"عمل")*(M4:M11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="N13" s="28">
-        <f>SUMPRODUCT((N4:N11&lt;&gt;"")*(N4:N11&lt;&gt;"عمل")*(N4:N11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="O13" s="28">
-        <f>SUMPRODUCT((O4:O11&lt;&gt;"")*(O4:O11&lt;&gt;"عمل")*(O4:O11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="P13" s="28">
-        <f>SUMPRODUCT((P4:P11&lt;&gt;"")*(P4:P11&lt;&gt;"عمل")*(P4:P11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="28">
-        <f>SUMPRODUCT((Q4:Q11&lt;&gt;"")*(Q4:Q11&lt;&gt;"عمل")*(Q4:Q11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="R13" s="28">
-        <f>SUMPRODUCT((R4:R11&lt;&gt;"")*(R4:R11&lt;&gt;"عمل")*(R4:R11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="S13" s="28">
-        <f>SUMPRODUCT((S4:S11&lt;&gt;"")*(S4:S11&lt;&gt;"عمل")*(S4:S11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="T13" s="28">
-        <f>SUMPRODUCT((T4:T11&lt;&gt;"")*(T4:T11&lt;&gt;"عمل")*(T4:T11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="U13" s="28">
-        <f>SUMPRODUCT((U4:U11&lt;&gt;"")*(U4:U11&lt;&gt;"عمل")*(U4:U11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="V13" s="28">
-        <f>SUMPRODUCT((V4:V11&lt;&gt;"")*(V4:V11&lt;&gt;"عمل")*(V4:V11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="W13" s="28">
-        <f>SUMPRODUCT((W4:W11&lt;&gt;"")*(W4:W11&lt;&gt;"عمل")*(W4:W11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="X13" s="28">
-        <f>SUMPRODUCT((X4:X11&lt;&gt;"")*(X4:X11&lt;&gt;"عمل")*(X4:X11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="Y13" s="28">
-        <f>SUMPRODUCT((Y4:Y11&lt;&gt;"")*(Y4:Y11&lt;&gt;"عمل")*(Y4:Y11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="Z13" s="28">
-        <f>SUMPRODUCT((Z4:Z11&lt;&gt;"")*(Z4:Z11&lt;&gt;"عمل")*(Z4:Z11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AA13" s="28">
-        <f>SUMPRODUCT((AA4:AA11&lt;&gt;"")*(AA4:AA11&lt;&gt;"عمل")*(AA4:AA11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AB13" s="28">
-        <f>SUMPRODUCT((AB4:AB11&lt;&gt;"")*(AB4:AB11&lt;&gt;"عمل")*(AB4:AB11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AC13" s="28">
-        <f>SUMPRODUCT((AC4:AC11&lt;&gt;"")*(AC4:AC11&lt;&gt;"عمل")*(AC4:AC11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AD13" s="28">
-        <f>SUMPRODUCT((AD4:AD11&lt;&gt;"")*(AD4:AD11&lt;&gt;"عمل")*(AD4:AD11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AE13" s="28">
-        <f>SUMPRODUCT((AE4:AE11&lt;&gt;"")*(AE4:AE11&lt;&gt;"عمل")*(AE4:AE11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AF13" s="28">
-        <f>SUMPRODUCT((AF4:AF11&lt;&gt;"")*(AF4:AF11&lt;&gt;"عمل")*(AF4:AF11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AG13" s="28">
-        <f>SUMPRODUCT((AG4:AG11&lt;&gt;"")*(AG4:AG11&lt;&gt;"عمل")*(AG4:AG11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-      <c r="AH13" s="28">
-        <f>SUMPRODUCT((AH4:AH11&lt;&gt;"")*(AH4:AH11&lt;&gt;"عمل")*(AH4:AH11&lt;&gt;"راحة"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="29" t="inlineStr">
+      <c r="D16" s="32">
+        <f>SUMPRODUCT((D4:D11&lt;&gt;"")*(D4:D11&lt;&gt;"صباح")*(D4:D11&lt;&gt;"عصر")*(D4:D11&lt;&gt;"ليل")*(D4:D11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>SUMPRODUCT((E4:E11&lt;&gt;"")*(E4:E11&lt;&gt;"صباح")*(E4:E11&lt;&gt;"عصر")*(E4:E11&lt;&gt;"ليل")*(E4:E11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>SUMPRODUCT((F4:F11&lt;&gt;"")*(F4:F11&lt;&gt;"صباح")*(F4:F11&lt;&gt;"عصر")*(F4:F11&lt;&gt;"ليل")*(F4:F11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>SUMPRODUCT((G4:G11&lt;&gt;"")*(G4:G11&lt;&gt;"صباح")*(G4:G11&lt;&gt;"عصر")*(G4:G11&lt;&gt;"ليل")*(G4:G11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>SUMPRODUCT((H4:H11&lt;&gt;"")*(H4:H11&lt;&gt;"صباح")*(H4:H11&lt;&gt;"عصر")*(H4:H11&lt;&gt;"ليل")*(H4:H11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="32">
+        <f>SUMPRODUCT((I4:I11&lt;&gt;"")*(I4:I11&lt;&gt;"صباح")*(I4:I11&lt;&gt;"عصر")*(I4:I11&lt;&gt;"ليل")*(I4:I11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="J16" s="32">
+        <f>SUMPRODUCT((J4:J11&lt;&gt;"")*(J4:J11&lt;&gt;"صباح")*(J4:J11&lt;&gt;"عصر")*(J4:J11&lt;&gt;"ليل")*(J4:J11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="K16" s="32">
+        <f>SUMPRODUCT((K4:K11&lt;&gt;"")*(K4:K11&lt;&gt;"صباح")*(K4:K11&lt;&gt;"عصر")*(K4:K11&lt;&gt;"ليل")*(K4:K11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="L16" s="32">
+        <f>SUMPRODUCT((L4:L11&lt;&gt;"")*(L4:L11&lt;&gt;"صباح")*(L4:L11&lt;&gt;"عصر")*(L4:L11&lt;&gt;"ليل")*(L4:L11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="M16" s="32">
+        <f>SUMPRODUCT((M4:M11&lt;&gt;"")*(M4:M11&lt;&gt;"صباح")*(M4:M11&lt;&gt;"عصر")*(M4:M11&lt;&gt;"ليل")*(M4:M11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="N16" s="32">
+        <f>SUMPRODUCT((N4:N11&lt;&gt;"")*(N4:N11&lt;&gt;"صباح")*(N4:N11&lt;&gt;"عصر")*(N4:N11&lt;&gt;"ليل")*(N4:N11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="O16" s="32">
+        <f>SUMPRODUCT((O4:O11&lt;&gt;"")*(O4:O11&lt;&gt;"صباح")*(O4:O11&lt;&gt;"عصر")*(O4:O11&lt;&gt;"ليل")*(O4:O11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="P16" s="32">
+        <f>SUMPRODUCT((P4:P11&lt;&gt;"")*(P4:P11&lt;&gt;"صباح")*(P4:P11&lt;&gt;"عصر")*(P4:P11&lt;&gt;"ليل")*(P4:P11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="32">
+        <f>SUMPRODUCT((Q4:Q11&lt;&gt;"")*(Q4:Q11&lt;&gt;"صباح")*(Q4:Q11&lt;&gt;"عصر")*(Q4:Q11&lt;&gt;"ليل")*(Q4:Q11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="R16" s="32">
+        <f>SUMPRODUCT((R4:R11&lt;&gt;"")*(R4:R11&lt;&gt;"صباح")*(R4:R11&lt;&gt;"عصر")*(R4:R11&lt;&gt;"ليل")*(R4:R11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="S16" s="32">
+        <f>SUMPRODUCT((S4:S11&lt;&gt;"")*(S4:S11&lt;&gt;"صباح")*(S4:S11&lt;&gt;"عصر")*(S4:S11&lt;&gt;"ليل")*(S4:S11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="T16" s="32">
+        <f>SUMPRODUCT((T4:T11&lt;&gt;"")*(T4:T11&lt;&gt;"صباح")*(T4:T11&lt;&gt;"عصر")*(T4:T11&lt;&gt;"ليل")*(T4:T11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="U16" s="32">
+        <f>SUMPRODUCT((U4:U11&lt;&gt;"")*(U4:U11&lt;&gt;"صباح")*(U4:U11&lt;&gt;"عصر")*(U4:U11&lt;&gt;"ليل")*(U4:U11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="V16" s="32">
+        <f>SUMPRODUCT((V4:V11&lt;&gt;"")*(V4:V11&lt;&gt;"صباح")*(V4:V11&lt;&gt;"عصر")*(V4:V11&lt;&gt;"ليل")*(V4:V11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="W16" s="32">
+        <f>SUMPRODUCT((W4:W11&lt;&gt;"")*(W4:W11&lt;&gt;"صباح")*(W4:W11&lt;&gt;"عصر")*(W4:W11&lt;&gt;"ليل")*(W4:W11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="X16" s="32">
+        <f>SUMPRODUCT((X4:X11&lt;&gt;"")*(X4:X11&lt;&gt;"صباح")*(X4:X11&lt;&gt;"عصر")*(X4:X11&lt;&gt;"ليل")*(X4:X11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="Y16" s="32">
+        <f>SUMPRODUCT((Y4:Y11&lt;&gt;"")*(Y4:Y11&lt;&gt;"صباح")*(Y4:Y11&lt;&gt;"عصر")*(Y4:Y11&lt;&gt;"ليل")*(Y4:Y11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="Z16" s="32">
+        <f>SUMPRODUCT((Z4:Z11&lt;&gt;"")*(Z4:Z11&lt;&gt;"صباح")*(Z4:Z11&lt;&gt;"عصر")*(Z4:Z11&lt;&gt;"ليل")*(Z4:Z11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AA16" s="32">
+        <f>SUMPRODUCT((AA4:AA11&lt;&gt;"")*(AA4:AA11&lt;&gt;"صباح")*(AA4:AA11&lt;&gt;"عصر")*(AA4:AA11&lt;&gt;"ليل")*(AA4:AA11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AB16" s="32">
+        <f>SUMPRODUCT((AB4:AB11&lt;&gt;"")*(AB4:AB11&lt;&gt;"صباح")*(AB4:AB11&lt;&gt;"عصر")*(AB4:AB11&lt;&gt;"ليل")*(AB4:AB11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AC16" s="32">
+        <f>SUMPRODUCT((AC4:AC11&lt;&gt;"")*(AC4:AC11&lt;&gt;"صباح")*(AC4:AC11&lt;&gt;"عصر")*(AC4:AC11&lt;&gt;"ليل")*(AC4:AC11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="32">
+        <f>SUMPRODUCT((AD4:AD11&lt;&gt;"")*(AD4:AD11&lt;&gt;"صباح")*(AD4:AD11&lt;&gt;"عصر")*(AD4:AD11&lt;&gt;"ليل")*(AD4:AD11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="32">
+        <f>SUMPRODUCT((AE4:AE11&lt;&gt;"")*(AE4:AE11&lt;&gt;"صباح")*(AE4:AE11&lt;&gt;"عصر")*(AE4:AE11&lt;&gt;"ليل")*(AE4:AE11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="32">
+        <f>SUMPRODUCT((AF4:AF11&lt;&gt;"")*(AF4:AF11&lt;&gt;"صباح")*(AF4:AF11&lt;&gt;"عصر")*(AF4:AF11&lt;&gt;"ليل")*(AF4:AF11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="32">
+        <f>SUMPRODUCT((AG4:AG11&lt;&gt;"")*(AG4:AG11&lt;&gt;"صباح")*(AG4:AG11&lt;&gt;"عصر")*(AG4:AG11&lt;&gt;"ليل")*(AG4:AG11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="32">
+        <f>SUMPRODUCT((AH4:AH11&lt;&gt;"")*(AH4:AH11&lt;&gt;"صباح")*(AH4:AH11&lt;&gt;"عصر")*(AH4:AH11&lt;&gt;"ليل")*(AH4:AH11&lt;&gt;"راحة"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>مفتاح الألوان:</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>عمل</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="31" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>صباح</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>عصر</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>ليل</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>راحة</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="32" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>سنوية</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="33" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>عارض</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="34" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>دورية</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="35" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>مرضية</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="45" t="inlineStr">
         <is>
           <t>مرافق مريض</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="37" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>أخرى</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D12">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="D15">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="E15">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="F15">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="G15">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="H15">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="I15">
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12">
-    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="J15">
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="K15">
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L12">
-    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="L15">
+    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M12">
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="M15">
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N12">
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="N15">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O12">
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="O15">
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P12">
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="P15">
+    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q12">
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="Q15">
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R12">
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="R15">
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S12">
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="S15">
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T12">
-    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="T15">
+    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U12">
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="U15">
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V12">
-    <cfRule type="cellIs" priority="19" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="V15">
+    <cfRule type="cellIs" priority="19" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W12">
-    <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="W15">
+    <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X12">
-    <cfRule type="cellIs" priority="21" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="X15">
+    <cfRule type="cellIs" priority="21" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y12">
-    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="Y15">
+    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z12">
-    <cfRule type="cellIs" priority="23" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="Z15">
+    <cfRule type="cellIs" priority="23" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA12">
-    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AA15">
+    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB12">
-    <cfRule type="cellIs" priority="25" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AB15">
+    <cfRule type="cellIs" priority="25" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC12">
-    <cfRule type="cellIs" priority="26" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AC15">
+    <cfRule type="cellIs" priority="26" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD12">
-    <cfRule type="cellIs" priority="27" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AD15">
+    <cfRule type="cellIs" priority="27" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE12">
-    <cfRule type="cellIs" priority="28" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AE15">
+    <cfRule type="cellIs" priority="28" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF12">
-    <cfRule type="cellIs" priority="29" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AF15">
+    <cfRule type="cellIs" priority="29" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG12">
-    <cfRule type="cellIs" priority="30" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AG15">
+    <cfRule type="cellIs" priority="30" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH12">
-    <cfRule type="cellIs" priority="31" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AH15">
+    <cfRule type="cellIs" priority="31" operator="lessThan" dxfId="3">
       <formula>'الإعدادات والقوائم'!$B$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:AH11">
-    <cfRule type="cellIs" priority="32" operator="equal" dxfId="9">
-      <formula>"عمل"</formula>
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
+      <formula>"صباح"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="33" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="1">
+      <formula>"عصر"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="2">
+      <formula>"ليل"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="12">
       <formula>"راحة"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="34" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="6">
       <formula>"سنوية"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="35" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="7">
       <formula>"عارض"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="36" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="8">
       <formula>"دورية"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="37" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="39" operator="equal" dxfId="9">
       <formula>"مرضية"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="38" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="40" operator="equal" dxfId="10">
       <formula>"مرافق مريض"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="39" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="41" operator="equal" dxfId="11">
       <formula>"أخرى"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/جدول_الورديات_وحجز_الإجازات.xlsx
+++ b/جدول_الورديات_وحجز_الإجازات.xlsx
@@ -12,6 +12,7 @@
     <sheet name="الموظفون" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="حجز الإجازات" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="جدول الورديات" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تقويم الإجازات" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="166" formatCode="DD/MM"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +95,12 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0044546A"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -196,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -325,6 +332,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -795,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B31"/>
+  <dimension ref="B1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -843,157 +854,164 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>3) حجز الإجازات: تُسجَّل فيه طلبات الإجازة، ويكشف التعارض تلقائياً.</t>
+          <t>3) تقويم الإجازات: عرض واضح للإجازات المعتمدة فقط (موظفون × أيام) مع إجمالي أيام كل موظف.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>4) الإعدادات والقوائم: ضبط بداية الدورة والحد الأدنى للتغطية وأنواع الإجازات.</t>
+          <t>4) حجز الإجازات: تُسجَّل فيه طلبات الإجازة، ويكشف التعارض تلقائياً.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>5) الإعدادات والقوائم: ضبط بداية الدورة والحد الأدنى للتغطية وأنواع الإجازات.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>نظام الدوام:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>• 6 أيام عمل متتالية ثم 4 أيام راحة (دورية) — دورة كل 10 أيام.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>• ثلاث ورديات (زامات):</t>
+          <t>• 6 أيام عمل متتالية ثم 4 أيام راحة (دورية) — دورة كل 10 أيام.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     صباح: 6:00 ص ← 1:00 م   |   عصر: 1:00 م ← 9:00 م   |   ليل: 9:00 م ← 6:00 ص (اليوم التالي).</t>
+          <t>• ثلاث ورديات (زامات):</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>• وردية كل موظف تُحدَّد من عمود «الوردية» في ورقة الموظفين (قابلة للتغيير).</t>
+          <t xml:space="preserve">     صباح: 6:00 ص ← 1:00 م   |   عصر: 1:00 م ← 9:00 م   |   ليل: 9:00 م ← 6:00 ص (اليوم التالي).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>• وردية كل موظف تُحدَّد من عمود «الوردية» في ورقة الموظفين (قابلة للتغيير).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>• الجدول يعرض اسم وردية الموظف على أيام عمله و«راحة» على أيام راحته — تلقائياً.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>أنواع الإجازات:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>سنوية • عارض • دورية • مرضية • مرافق مريض • أخرى</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>كيف أحجز إجازة بدون تعارض؟</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>1) افتح ورقة «حجز الإجازات».</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2) اختر اسم الموظف ونوع الإجازة من القائمة المنسدلة، وأدخل تاريخ البداية والنهاية.</t>
+          <t>1) افتح ورقة «حجز الإجازات».</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>3) عمود «عدد الأيام» يُحسب تلقائياً، وعمود «فحص التعارض» يتحقق فوراً:</t>
+          <t>2) اختر اسم الموظف ونوع الإجازة من القائمة المنسدلة، وأدخل تاريخ البداية والنهاية.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     ✓ سليم = لا يوجد تعارض   |   ⚠ تعارض = للموظف إجازة أخرى متداخلة بنفس الفترة.</t>
+          <t>3) عمود «عدد الأيام» يُحسب تلقائياً، وعمود «فحص التعارض» يتحقق فوراً:</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>4) عمود «تنبيه التغطية» ينبّه إذا تجاوز عدد المُجازين في نفس اليوم الحد المسموح.</t>
+          <t xml:space="preserve">     ✓ سليم = لا يوجد تعارض   |   ⚠ تعارض = للموظف إجازة أخرى متداخلة بنفس الفترة.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>4) عمود «تنبيه التغطية» ينبّه إذا تجاوز عدد المُجازين في نفس اليوم الحد المسموح.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>5) غيّر «الحالة» إلى «معتمد» لتظهر الإجازة ملوّنة في جدول الورديات.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>ملاحظات:</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>• الصفوف الحمراء/التنبيهات تعني وجود تعارض — عالجه قبل الاعتماد.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>• في «جدول الورديات» يظهر أسفل كل يوم: عدد العاملين وعدد المُجازين؛ ويتلوّن بالأحمر عند نقص التغطية.</t>
+          <t>• الصفوف الحمراء/التنبيهات تعني وجود تعارض — عالجه قبل الاعتماد.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>• في «جدول الورديات» يظهر أسفل كل يوم: عدد العاملين وعدد المُجازين؛ ويتلوّن بالأحمر عند نقص التغطية.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>• كل التواريخ بصيغة يوم/شهر/سنة. عدّل «بداية الفترة» وعدد الموظفين بحرية.</t>
         </is>
@@ -1503,15 +1521,31 @@
       <c r="A5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>سالم شليويح المري</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>دورية</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>46192</v>
+      </c>
       <c r="F5" s="20">
         <f>IF(OR($D5="",$E5=""),"",$E5-$D5+1)</f>
         <v/>
       </c>
-      <c r="G5" s="20" t="n"/>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H5" s="20">
         <f>IF(OR($B5="",$D5="",$E5=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B5)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B5&lt;&gt;"")*($G5&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1526,15 +1560,31 @@
       <c r="A6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="25" t="n"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>فهد عبدالعزيز عبدالله</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>46192</v>
+      </c>
       <c r="F6" s="20">
         <f>IF(OR($D6="",$E6=""),"",$E6-$D6+1)</f>
         <v/>
       </c>
-      <c r="G6" s="20" t="n"/>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H6" s="20">
         <f>IF(OR($B6="",$D6="",$E6=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B6)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B6&lt;&gt;"")*($G6&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1549,15 +1599,31 @@
       <c r="A7" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="25" t="n"/>
-      <c r="E7" s="25" t="n"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>محمد ناصر الغانم</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>دورية</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>46205</v>
+      </c>
       <c r="F7" s="20">
         <f>IF(OR($D7="",$E7=""),"",$E7-$D7+1)</f>
         <v/>
       </c>
-      <c r="G7" s="20" t="n"/>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H7" s="20">
         <f>IF(OR($B7="",$D7="",$E7=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B7)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B7&lt;&gt;"")*($G7&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1572,15 +1638,31 @@
       <c r="A8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="25" t="n"/>
-      <c r="E8" s="25" t="n"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>محمد ناصر الغانم</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>دورية</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>46208</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>46212</v>
+      </c>
       <c r="F8" s="20">
         <f>IF(OR($D8="",$E8=""),"",$E8-$D8+1)</f>
         <v/>
       </c>
-      <c r="G8" s="20" t="n"/>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H8" s="20">
         <f>IF(OR($B8="",$D8="",$E8=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B8)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B8&lt;&gt;"")*($G8&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1595,15 +1677,31 @@
       <c r="A9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="25" t="n"/>
-      <c r="E9" s="25" t="n"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>منصور مبارك الجابري</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>46212</v>
+      </c>
       <c r="F9" s="20">
         <f>IF(OR($D9="",$E9=""),"",$E9-$D9+1)</f>
         <v/>
       </c>
-      <c r="G9" s="20" t="n"/>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H9" s="20">
         <f>IF(OR($B9="",$D9="",$E9=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B9)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B9&lt;&gt;"")*($G9&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1618,15 +1716,31 @@
       <c r="A10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="25" t="n"/>
-      <c r="E10" s="25" t="n"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>منصور مبارك الجابري</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>46192</v>
+      </c>
       <c r="F10" s="20">
         <f>IF(OR($D10="",$E10=""),"",$E10-$D10+1)</f>
         <v/>
       </c>
-      <c r="G10" s="20" t="n"/>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H10" s="20">
         <f>IF(OR($B10="",$D10="",$E10=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B10)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B10&lt;&gt;"")*($G10&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1641,15 +1755,31 @@
       <c r="A11" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>محمد حمد الجابر</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>46192</v>
+      </c>
       <c r="F11" s="20">
         <f>IF(OR($D11="",$E11=""),"",$E11-$D11+1)</f>
         <v/>
       </c>
-      <c r="G11" s="20" t="n"/>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H11" s="20">
         <f>IF(OR($B11="",$D11="",$E11=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B11)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B11&lt;&gt;"")*($G11&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1664,15 +1794,31 @@
       <c r="A12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>عبدالله سعد المهندي</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>مرافق مريض</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>46233</v>
+      </c>
       <c r="F12" s="20">
         <f>IF(OR($D12="",$E12=""),"",$E12-$D12+1)</f>
         <v/>
       </c>
-      <c r="G12" s="20" t="n"/>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H12" s="20">
         <f>IF(OR($B12="",$D12="",$E12=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B12)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B12&lt;&gt;"")*($G12&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1687,15 +1833,31 @@
       <c r="A13" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>راشد عيسى التميمي</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>46212</v>
+      </c>
       <c r="F13" s="20">
         <f>IF(OR($D13="",$E13=""),"",$E13-$D13+1)</f>
         <v/>
       </c>
-      <c r="G13" s="20" t="n"/>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H13" s="20">
         <f>IF(OR($B13="",$D13="",$E13=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B13)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B13&lt;&gt;"")*($G13&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1710,15 +1872,31 @@
       <c r="A14" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>راشد عيسى التميمي</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>عارض</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>46217</v>
+      </c>
       <c r="F14" s="20">
         <f>IF(OR($D14="",$E14=""),"",$E14-$D14+1)</f>
         <v/>
       </c>
-      <c r="G14" s="20" t="n"/>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H14" s="20">
         <f>IF(OR($B14="",$D14="",$E14=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B14)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B14&lt;&gt;"")*($G14&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1733,15 +1911,31 @@
       <c r="A15" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>راشد عيسى التميمي</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>46222</v>
+      </c>
       <c r="F15" s="20">
         <f>IF(OR($D15="",$E15=""),"",$E15-$D15+1)</f>
         <v/>
       </c>
-      <c r="G15" s="20" t="n"/>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H15" s="20">
         <f>IF(OR($B15="",$D15="",$E15=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B15)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B15&lt;&gt;"")*($G15&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -1756,15 +1950,31 @@
       <c r="A16" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>راشد عيسى التميمي</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>أخرى</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>46190</v>
+      </c>
       <c r="F16" s="20">
         <f>IF(OR($D16="",$E16=""),"",$E16-$D16+1)</f>
         <v/>
       </c>
-      <c r="G16" s="20" t="n"/>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>معتمد</t>
+        </is>
+      </c>
       <c r="H16" s="20">
         <f>IF(OR($B16="",$D16="",$E16=""),"",IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104=$B16)*('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$E16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))-(($B16&lt;&gt;"")*($G16&lt;&gt;"مرفوض"))&gt;0,"⚠ تعارض","✓ سليم"))</f>
         <v/>
@@ -6190,4 +6400,1822 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="25" max="25"/>
+    <col width="6" customWidth="1" min="26" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="6" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="32" max="32"/>
+    <col width="6" customWidth="1" min="33" max="33"/>
+    <col width="6" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>تقويم الإجازات — يعرض الإجازات المعتمدة فقط بألوانها</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="47" t="inlineStr">
+        <is>
+          <t>كل خلية ملوّنة = إجازة معتمدة لذلك اليوم. الخلايا الفارغة = لا توجد إجازة.</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>الثلاثاء</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>الخميس</t>
+        </is>
+      </c>
+      <c r="G2" s="27" t="inlineStr">
+        <is>
+          <t>الجمعة</t>
+        </is>
+      </c>
+      <c r="H2" s="27" t="inlineStr">
+        <is>
+          <t>السبت</t>
+        </is>
+      </c>
+      <c r="I2" s="27" t="inlineStr">
+        <is>
+          <t>الأحد</t>
+        </is>
+      </c>
+      <c r="J2" s="27" t="inlineStr">
+        <is>
+          <t>الإثنين</t>
+        </is>
+      </c>
+      <c r="K2" s="27" t="inlineStr">
+        <is>
+          <t>الثلاثاء</t>
+        </is>
+      </c>
+      <c r="L2" s="27" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="M2" s="27" t="inlineStr">
+        <is>
+          <t>الخميس</t>
+        </is>
+      </c>
+      <c r="N2" s="27" t="inlineStr">
+        <is>
+          <t>الجمعة</t>
+        </is>
+      </c>
+      <c r="O2" s="27" t="inlineStr">
+        <is>
+          <t>السبت</t>
+        </is>
+      </c>
+      <c r="P2" s="27" t="inlineStr">
+        <is>
+          <t>الأحد</t>
+        </is>
+      </c>
+      <c r="Q2" s="27" t="inlineStr">
+        <is>
+          <t>الإثنين</t>
+        </is>
+      </c>
+      <c r="R2" s="27" t="inlineStr">
+        <is>
+          <t>الثلاثاء</t>
+        </is>
+      </c>
+      <c r="S2" s="27" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="T2" s="27" t="inlineStr">
+        <is>
+          <t>الخميس</t>
+        </is>
+      </c>
+      <c r="U2" s="27" t="inlineStr">
+        <is>
+          <t>الجمعة</t>
+        </is>
+      </c>
+      <c r="V2" s="27" t="inlineStr">
+        <is>
+          <t>السبت</t>
+        </is>
+      </c>
+      <c r="W2" s="27" t="inlineStr">
+        <is>
+          <t>الأحد</t>
+        </is>
+      </c>
+      <c r="X2" s="27" t="inlineStr">
+        <is>
+          <t>الإثنين</t>
+        </is>
+      </c>
+      <c r="Y2" s="27" t="inlineStr">
+        <is>
+          <t>الثلاثاء</t>
+        </is>
+      </c>
+      <c r="Z2" s="27" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="AA2" s="27" t="inlineStr">
+        <is>
+          <t>الخميس</t>
+        </is>
+      </c>
+      <c r="AB2" s="27" t="inlineStr">
+        <is>
+          <t>الجمعة</t>
+        </is>
+      </c>
+      <c r="AC2" s="27" t="inlineStr">
+        <is>
+          <t>السبت</t>
+        </is>
+      </c>
+      <c r="AD2" s="27" t="inlineStr">
+        <is>
+          <t>الأحد</t>
+        </is>
+      </c>
+      <c r="AE2" s="27" t="inlineStr">
+        <is>
+          <t>الإثنين</t>
+        </is>
+      </c>
+      <c r="AF2" s="27" t="inlineStr">
+        <is>
+          <t>الثلاثاء</t>
+        </is>
+      </c>
+      <c r="AG2" s="27" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="AH2" s="27" t="inlineStr">
+        <is>
+          <t>الخميس</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>الاسم</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>الرقم الوظيفي</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>46190</v>
+      </c>
+      <c r="F3" s="28" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G3" s="29" t="n">
+        <v>46192</v>
+      </c>
+      <c r="H3" s="28" t="n">
+        <v>46193</v>
+      </c>
+      <c r="I3" s="28" t="n">
+        <v>46194</v>
+      </c>
+      <c r="J3" s="28" t="n">
+        <v>46195</v>
+      </c>
+      <c r="K3" s="28" t="n">
+        <v>46196</v>
+      </c>
+      <c r="L3" s="28" t="n">
+        <v>46197</v>
+      </c>
+      <c r="M3" s="28" t="n">
+        <v>46198</v>
+      </c>
+      <c r="N3" s="29" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>46200</v>
+      </c>
+      <c r="P3" s="28" t="n">
+        <v>46201</v>
+      </c>
+      <c r="Q3" s="28" t="n">
+        <v>46202</v>
+      </c>
+      <c r="R3" s="28" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S3" s="28" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T3" s="28" t="n">
+        <v>46205</v>
+      </c>
+      <c r="U3" s="29" t="n">
+        <v>46206</v>
+      </c>
+      <c r="V3" s="28" t="n">
+        <v>46207</v>
+      </c>
+      <c r="W3" s="28" t="n">
+        <v>46208</v>
+      </c>
+      <c r="X3" s="28" t="n">
+        <v>46209</v>
+      </c>
+      <c r="Y3" s="28" t="n">
+        <v>46210</v>
+      </c>
+      <c r="Z3" s="28" t="n">
+        <v>46211</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>46212</v>
+      </c>
+      <c r="AB3" s="29" t="n">
+        <v>46213</v>
+      </c>
+      <c r="AC3" s="28" t="n">
+        <v>46214</v>
+      </c>
+      <c r="AD3" s="28" t="n">
+        <v>46215</v>
+      </c>
+      <c r="AE3" s="28" t="n">
+        <v>46216</v>
+      </c>
+      <c r="AF3" s="28" t="n">
+        <v>46217</v>
+      </c>
+      <c r="AG3" s="28" t="n">
+        <v>46218</v>
+      </c>
+      <c r="AH3" s="28" t="n">
+        <v>46219</v>
+      </c>
+      <c r="AI3" s="6" t="inlineStr">
+        <is>
+          <t>إجمالي الأيام</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21">
+        <f>'الموظفون'!B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="20">
+        <f>'الموظفون'!C2</f>
+        <v/>
+      </c>
+      <c r="D4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH4" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI4" s="48">
+        <f>SUMPRODUCT(--(D4:AH4&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="21">
+        <f>'الموظفون'!B3</f>
+        <v/>
+      </c>
+      <c r="C5" s="20">
+        <f>'الموظفون'!C3</f>
+        <v/>
+      </c>
+      <c r="D5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH5" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI5" s="48">
+        <f>SUMPRODUCT(--(D5:AH5&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21">
+        <f>'الموظفون'!B4</f>
+        <v/>
+      </c>
+      <c r="C6" s="20">
+        <f>'الموظفون'!C4</f>
+        <v/>
+      </c>
+      <c r="D6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH6" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI6" s="48">
+        <f>SUMPRODUCT(--(D6:AH6&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="21">
+        <f>'الموظفون'!B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="20">
+        <f>'الموظفون'!C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH7" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI7" s="48">
+        <f>SUMPRODUCT(--(D7:AH7&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="21">
+        <f>'الموظفون'!B6</f>
+        <v/>
+      </c>
+      <c r="C8" s="20">
+        <f>'الموظفون'!C6</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="48">
+        <f>SUMPRODUCT(--(D8:AH8&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="21">
+        <f>'الموظفون'!B7</f>
+        <v/>
+      </c>
+      <c r="C9" s="20">
+        <f>'الموظفون'!C7</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="48">
+        <f>SUMPRODUCT(--(D9:AH9&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="21">
+        <f>'الموظفون'!B8</f>
+        <v/>
+      </c>
+      <c r="C10" s="20">
+        <f>'الموظفون'!C8</f>
+        <v/>
+      </c>
+      <c r="D10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="48">
+        <f>SUMPRODUCT(--(D10:AH10&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="21">
+        <f>'الموظفون'!B9</f>
+        <v/>
+      </c>
+      <c r="C11" s="20">
+        <f>'الموظفون'!C9</f>
+        <v/>
+      </c>
+      <c r="D11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="I11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="J11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="K11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="L11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="M11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="N11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="O11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="P11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="R11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="S11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="T11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="U11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="V11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="W11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="X11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Y11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="Z11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AA11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AC11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AD11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AH11" s="30">
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,"",INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="48">
+        <f>SUMPRODUCT(--(D11:AH11&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>عدد المُجازين</t>
+        </is>
+      </c>
+      <c r="D12" s="32">
+        <f>SUMPRODUCT(--(D4:D11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>SUMPRODUCT(--(E4:E11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>SUMPRODUCT(--(F4:F11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G12" s="32">
+        <f>SUMPRODUCT(--(G4:G11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="H12" s="32">
+        <f>SUMPRODUCT(--(H4:H11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="I12" s="32">
+        <f>SUMPRODUCT(--(I4:I11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="J12" s="32">
+        <f>SUMPRODUCT(--(J4:J11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="K12" s="32">
+        <f>SUMPRODUCT(--(K4:K11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="L12" s="32">
+        <f>SUMPRODUCT(--(L4:L11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="M12" s="32">
+        <f>SUMPRODUCT(--(M4:M11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="N12" s="32">
+        <f>SUMPRODUCT(--(N4:N11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="O12" s="32">
+        <f>SUMPRODUCT(--(O4:O11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="P12" s="32">
+        <f>SUMPRODUCT(--(P4:P11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="32">
+        <f>SUMPRODUCT(--(Q4:Q11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="R12" s="32">
+        <f>SUMPRODUCT(--(R4:R11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="S12" s="32">
+        <f>SUMPRODUCT(--(S4:S11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="T12" s="32">
+        <f>SUMPRODUCT(--(T4:T11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="U12" s="32">
+        <f>SUMPRODUCT(--(U4:U11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="V12" s="32">
+        <f>SUMPRODUCT(--(V4:V11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="W12" s="32">
+        <f>SUMPRODUCT(--(W4:W11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="X12" s="32">
+        <f>SUMPRODUCT(--(X4:X11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Y12" s="32">
+        <f>SUMPRODUCT(--(Y4:Y11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Z12" s="32">
+        <f>SUMPRODUCT(--(Z4:Z11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AA12" s="32">
+        <f>SUMPRODUCT(--(AA4:AA11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="32">
+        <f>SUMPRODUCT(--(AB4:AB11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AC12" s="32">
+        <f>SUMPRODUCT(--(AC4:AC11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="32">
+        <f>SUMPRODUCT(--(AD4:AD11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="32">
+        <f>SUMPRODUCT(--(AE4:AE11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="32">
+        <f>SUMPRODUCT(--(AF4:AF11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="32">
+        <f>SUMPRODUCT(--(AG4:AG11&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="32">
+        <f>SUMPRODUCT(--(AH4:AH11&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>مفتاح ألوان الإجازات:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>عارض</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>دورية</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>مرضية</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>مرافق مريض</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>أخرى</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L12">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M12">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N12">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O12">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P12">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q12">
+    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R12">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S12">
+    <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T12">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U12">
+    <cfRule type="cellIs" priority="18" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V12">
+    <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W12">
+    <cfRule type="cellIs" priority="20" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X12">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y12">
+    <cfRule type="cellIs" priority="22" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z12">
+    <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA12">
+    <cfRule type="cellIs" priority="24" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB12">
+    <cfRule type="cellIs" priority="25" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC12">
+    <cfRule type="cellIs" priority="26" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD12">
+    <cfRule type="cellIs" priority="27" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE12">
+    <cfRule type="cellIs" priority="28" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF12">
+    <cfRule type="cellIs" priority="29" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG12">
+    <cfRule type="cellIs" priority="30" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH12">
+    <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="3">
+      <formula>'الإعدادات والقوائم'!$B$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:AH11">
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="6">
+      <formula>"سنوية"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="7">
+      <formula>"عارض"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="8">
+      <formula>"دورية"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="9">
+      <formula>"مرضية"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="10">
+      <formula>"مرافق مريض"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="11">
+      <formula>"أخرى"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/جدول_الورديات_وحجز_الإجازات.xlsx
+++ b/جدول_الورديات_وحجز_الإجازات.xlsx
@@ -14,8 +14,13 @@
     <sheet name="جدول الورديات" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تقويم الإجازات" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="CycleWork">'الإعدادات والقوائم'!$B$3</definedName>
+    <definedName name="CycleRest">'الإعدادات والقوائم'!$B$4</definedName>
+    <definedName name="MinStaff">'الإعدادات والقوائم'!$B$5</definedName>
+    <definedName name="MaxLeave">'الإعدادات والقوائم'!$B$6</definedName>
+  </definedNames>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1551,7 +1556,7 @@
         <v/>
       </c>
       <c r="I5" s="20">
-        <f>IF($D5="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D5="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D5)*($D5&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J5" s="21" t="n"/>
@@ -1590,7 +1595,7 @@
         <v/>
       </c>
       <c r="I6" s="20">
-        <f>IF($D6="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D6="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D6)*($D6&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J6" s="21" t="n"/>
@@ -1629,7 +1634,7 @@
         <v/>
       </c>
       <c r="I7" s="20">
-        <f>IF($D7="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D7="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D7)*($D7&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J7" s="21" t="n"/>
@@ -1668,7 +1673,7 @@
         <v/>
       </c>
       <c r="I8" s="20">
-        <f>IF($D8="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D8="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D8)*($D8&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J8" s="21" t="n"/>
@@ -1707,7 +1712,7 @@
         <v/>
       </c>
       <c r="I9" s="20">
-        <f>IF($D9="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D9="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D9)*($D9&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J9" s="21" t="n"/>
@@ -1746,7 +1751,7 @@
         <v/>
       </c>
       <c r="I10" s="20">
-        <f>IF($D10="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D10="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D10)*($D10&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J10" s="21" t="n"/>
@@ -1785,7 +1790,7 @@
         <v/>
       </c>
       <c r="I11" s="20">
-        <f>IF($D11="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D11="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D11)*($D11&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J11" s="21" t="n"/>
@@ -1824,7 +1829,7 @@
         <v/>
       </c>
       <c r="I12" s="20">
-        <f>IF($D12="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D12="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D12)*($D12&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J12" s="21" t="n"/>
@@ -1863,7 +1868,7 @@
         <v/>
       </c>
       <c r="I13" s="20">
-        <f>IF($D13="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D13="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D13)*($D13&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J13" s="21" t="n"/>
@@ -1902,7 +1907,7 @@
         <v/>
       </c>
       <c r="I14" s="20">
-        <f>IF($D14="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D14="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D14)*($D14&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J14" s="21" t="n"/>
@@ -1941,7 +1946,7 @@
         <v/>
       </c>
       <c r="I15" s="20">
-        <f>IF($D15="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D15="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D15)*($D15&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J15" s="21" t="n"/>
@@ -1980,7 +1985,7 @@
         <v/>
       </c>
       <c r="I16" s="20">
-        <f>IF($D16="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D16="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D16)*($D16&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J16" s="21" t="n"/>
@@ -2003,7 +2008,7 @@
         <v/>
       </c>
       <c r="I17" s="20">
-        <f>IF($D17="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D17="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D17)*($D17&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J17" s="21" t="n"/>
@@ -2026,7 +2031,7 @@
         <v/>
       </c>
       <c r="I18" s="20">
-        <f>IF($D18="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D18="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D18)*($D18&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J18" s="21" t="n"/>
@@ -2049,7 +2054,7 @@
         <v/>
       </c>
       <c r="I19" s="20">
-        <f>IF($D19="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D19="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D19)*($D19&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J19" s="21" t="n"/>
@@ -2072,7 +2077,7 @@
         <v/>
       </c>
       <c r="I20" s="20">
-        <f>IF($D20="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D20="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D20)*($D20&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J20" s="21" t="n"/>
@@ -2095,7 +2100,7 @@
         <v/>
       </c>
       <c r="I21" s="20">
-        <f>IF($D21="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D21="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D21)*($D21&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J21" s="21" t="n"/>
@@ -2118,7 +2123,7 @@
         <v/>
       </c>
       <c r="I22" s="20">
-        <f>IF($D22="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D22="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D22)*($D22&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J22" s="21" t="n"/>
@@ -2141,7 +2146,7 @@
         <v/>
       </c>
       <c r="I23" s="20">
-        <f>IF($D23="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D23="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D23)*($D23&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J23" s="21" t="n"/>
@@ -2164,7 +2169,7 @@
         <v/>
       </c>
       <c r="I24" s="20">
-        <f>IF($D24="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D24="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D24)*($D24&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J24" s="21" t="n"/>
@@ -2187,7 +2192,7 @@
         <v/>
       </c>
       <c r="I25" s="20">
-        <f>IF($D25="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D25="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D25)*($D25&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J25" s="21" t="n"/>
@@ -2210,7 +2215,7 @@
         <v/>
       </c>
       <c r="I26" s="20">
-        <f>IF($D26="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D26="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D26)*($D26&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J26" s="21" t="n"/>
@@ -2233,7 +2238,7 @@
         <v/>
       </c>
       <c r="I27" s="20">
-        <f>IF($D27="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D27="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D27)*($D27&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J27" s="21" t="n"/>
@@ -2256,7 +2261,7 @@
         <v/>
       </c>
       <c r="I28" s="20">
-        <f>IF($D28="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D28="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D28)*($D28&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J28" s="21" t="n"/>
@@ -2279,7 +2284,7 @@
         <v/>
       </c>
       <c r="I29" s="20">
-        <f>IF($D29="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D29="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D29)*($D29&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J29" s="21" t="n"/>
@@ -2302,7 +2307,7 @@
         <v/>
       </c>
       <c r="I30" s="20">
-        <f>IF($D30="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D30="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D30)*($D30&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J30" s="21" t="n"/>
@@ -2325,7 +2330,7 @@
         <v/>
       </c>
       <c r="I31" s="20">
-        <f>IF($D31="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D31="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D31)*($D31&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J31" s="21" t="n"/>
@@ -2348,7 +2353,7 @@
         <v/>
       </c>
       <c r="I32" s="20">
-        <f>IF($D32="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D32="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D32)*($D32&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J32" s="21" t="n"/>
@@ -2371,7 +2376,7 @@
         <v/>
       </c>
       <c r="I33" s="20">
-        <f>IF($D33="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D33="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D33)*($D33&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J33" s="21" t="n"/>
@@ -2394,7 +2399,7 @@
         <v/>
       </c>
       <c r="I34" s="20">
-        <f>IF($D34="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D34="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D34)*($D34&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J34" s="21" t="n"/>
@@ -2417,7 +2422,7 @@
         <v/>
       </c>
       <c r="I35" s="20">
-        <f>IF($D35="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D35="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D35)*($D35&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J35" s="21" t="n"/>
@@ -2440,7 +2445,7 @@
         <v/>
       </c>
       <c r="I36" s="20">
-        <f>IF($D36="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D36="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D36)*($D36&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J36" s="21" t="n"/>
@@ -2463,7 +2468,7 @@
         <v/>
       </c>
       <c r="I37" s="20">
-        <f>IF($D37="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D37="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D37)*($D37&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J37" s="21" t="n"/>
@@ -2486,7 +2491,7 @@
         <v/>
       </c>
       <c r="I38" s="20">
-        <f>IF($D38="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D38="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D38)*($D38&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J38" s="21" t="n"/>
@@ -2509,7 +2514,7 @@
         <v/>
       </c>
       <c r="I39" s="20">
-        <f>IF($D39="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D39="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D39)*($D39&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J39" s="21" t="n"/>
@@ -2532,7 +2537,7 @@
         <v/>
       </c>
       <c r="I40" s="20">
-        <f>IF($D40="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D40="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D40)*($D40&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J40" s="21" t="n"/>
@@ -2555,7 +2560,7 @@
         <v/>
       </c>
       <c r="I41" s="20">
-        <f>IF($D41="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D41="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D41)*($D41&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J41" s="21" t="n"/>
@@ -2578,7 +2583,7 @@
         <v/>
       </c>
       <c r="I42" s="20">
-        <f>IF($D42="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D42="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D42)*($D42&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J42" s="21" t="n"/>
@@ -2601,7 +2606,7 @@
         <v/>
       </c>
       <c r="I43" s="20">
-        <f>IF($D43="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D43="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D43)*($D43&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J43" s="21" t="n"/>
@@ -2624,7 +2629,7 @@
         <v/>
       </c>
       <c r="I44" s="20">
-        <f>IF($D44="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D44="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D44)*($D44&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J44" s="21" t="n"/>
@@ -2647,7 +2652,7 @@
         <v/>
       </c>
       <c r="I45" s="20">
-        <f>IF($D45="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D45="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D45)*($D45&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J45" s="21" t="n"/>
@@ -2670,7 +2675,7 @@
         <v/>
       </c>
       <c r="I46" s="20">
-        <f>IF($D46="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D46="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D46)*($D46&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J46" s="21" t="n"/>
@@ -2693,7 +2698,7 @@
         <v/>
       </c>
       <c r="I47" s="20">
-        <f>IF($D47="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D47="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D47)*($D47&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J47" s="21" t="n"/>
@@ -2716,7 +2721,7 @@
         <v/>
       </c>
       <c r="I48" s="20">
-        <f>IF($D48="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D48="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D48)*($D48&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J48" s="21" t="n"/>
@@ -2739,7 +2744,7 @@
         <v/>
       </c>
       <c r="I49" s="20">
-        <f>IF($D49="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D49="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D49)*($D49&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J49" s="21" t="n"/>
@@ -2762,7 +2767,7 @@
         <v/>
       </c>
       <c r="I50" s="20">
-        <f>IF($D50="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D50="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D50)*($D50&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J50" s="21" t="n"/>
@@ -2785,7 +2790,7 @@
         <v/>
       </c>
       <c r="I51" s="20">
-        <f>IF($D51="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D51="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D51)*($D51&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J51" s="21" t="n"/>
@@ -2808,7 +2813,7 @@
         <v/>
       </c>
       <c r="I52" s="20">
-        <f>IF($D52="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D52="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D52)*($D52&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J52" s="21" t="n"/>
@@ -2831,7 +2836,7 @@
         <v/>
       </c>
       <c r="I53" s="20">
-        <f>IF($D53="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D53="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D53)*($D53&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J53" s="21" t="n"/>
@@ -2854,7 +2859,7 @@
         <v/>
       </c>
       <c r="I54" s="20">
-        <f>IF($D54="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D54="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D54)*($D54&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J54" s="21" t="n"/>
@@ -2877,7 +2882,7 @@
         <v/>
       </c>
       <c r="I55" s="20">
-        <f>IF($D55="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D55="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D55)*($D55&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J55" s="21" t="n"/>
@@ -2900,7 +2905,7 @@
         <v/>
       </c>
       <c r="I56" s="20">
-        <f>IF($D56="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D56="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D56)*($D56&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J56" s="21" t="n"/>
@@ -2923,7 +2928,7 @@
         <v/>
       </c>
       <c r="I57" s="20">
-        <f>IF($D57="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D57="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D57)*($D57&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J57" s="21" t="n"/>
@@ -2946,7 +2951,7 @@
         <v/>
       </c>
       <c r="I58" s="20">
-        <f>IF($D58="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D58="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D58)*($D58&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J58" s="21" t="n"/>
@@ -2969,7 +2974,7 @@
         <v/>
       </c>
       <c r="I59" s="20">
-        <f>IF($D59="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D59="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D59)*($D59&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J59" s="21" t="n"/>
@@ -2992,7 +2997,7 @@
         <v/>
       </c>
       <c r="I60" s="20">
-        <f>IF($D60="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D60="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D60)*($D60&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J60" s="21" t="n"/>
@@ -3015,7 +3020,7 @@
         <v/>
       </c>
       <c r="I61" s="20">
-        <f>IF($D61="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D61="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D61)*($D61&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J61" s="21" t="n"/>
@@ -3038,7 +3043,7 @@
         <v/>
       </c>
       <c r="I62" s="20">
-        <f>IF($D62="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D62="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D62)*($D62&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J62" s="21" t="n"/>
@@ -3061,7 +3066,7 @@
         <v/>
       </c>
       <c r="I63" s="20">
-        <f>IF($D63="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D63="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D63)*($D63&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J63" s="21" t="n"/>
@@ -3084,7 +3089,7 @@
         <v/>
       </c>
       <c r="I64" s="20">
-        <f>IF($D64="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D64="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D64)*($D64&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J64" s="21" t="n"/>
@@ -3107,7 +3112,7 @@
         <v/>
       </c>
       <c r="I65" s="20">
-        <f>IF($D65="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D65="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D65)*($D65&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J65" s="21" t="n"/>
@@ -3130,7 +3135,7 @@
         <v/>
       </c>
       <c r="I66" s="20">
-        <f>IF($D66="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D66="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D66)*($D66&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J66" s="21" t="n"/>
@@ -3153,7 +3158,7 @@
         <v/>
       </c>
       <c r="I67" s="20">
-        <f>IF($D67="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D67="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D67)*($D67&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J67" s="21" t="n"/>
@@ -3176,7 +3181,7 @@
         <v/>
       </c>
       <c r="I68" s="20">
-        <f>IF($D68="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D68="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D68)*($D68&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J68" s="21" t="n"/>
@@ -3199,7 +3204,7 @@
         <v/>
       </c>
       <c r="I69" s="20">
-        <f>IF($D69="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D69="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D69)*($D69&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J69" s="21" t="n"/>
@@ -3222,7 +3227,7 @@
         <v/>
       </c>
       <c r="I70" s="20">
-        <f>IF($D70="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D70="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D70)*($D70&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J70" s="21" t="n"/>
@@ -3245,7 +3250,7 @@
         <v/>
       </c>
       <c r="I71" s="20">
-        <f>IF($D71="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D71="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D71)*($D71&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J71" s="21" t="n"/>
@@ -3268,7 +3273,7 @@
         <v/>
       </c>
       <c r="I72" s="20">
-        <f>IF($D72="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D72="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D72)*($D72&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J72" s="21" t="n"/>
@@ -3291,7 +3296,7 @@
         <v/>
       </c>
       <c r="I73" s="20">
-        <f>IF($D73="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D73="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D73)*($D73&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J73" s="21" t="n"/>
@@ -3314,7 +3319,7 @@
         <v/>
       </c>
       <c r="I74" s="20">
-        <f>IF($D74="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D74="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D74)*($D74&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J74" s="21" t="n"/>
@@ -3337,7 +3342,7 @@
         <v/>
       </c>
       <c r="I75" s="20">
-        <f>IF($D75="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D75="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D75)*($D75&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J75" s="21" t="n"/>
@@ -3360,7 +3365,7 @@
         <v/>
       </c>
       <c r="I76" s="20">
-        <f>IF($D76="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D76="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D76)*($D76&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J76" s="21" t="n"/>
@@ -3383,7 +3388,7 @@
         <v/>
       </c>
       <c r="I77" s="20">
-        <f>IF($D77="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D77="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D77)*($D77&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J77" s="21" t="n"/>
@@ -3406,7 +3411,7 @@
         <v/>
       </c>
       <c r="I78" s="20">
-        <f>IF($D78="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D78="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D78)*($D78&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J78" s="21" t="n"/>
@@ -3429,7 +3434,7 @@
         <v/>
       </c>
       <c r="I79" s="20">
-        <f>IF($D79="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D79="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D79)*($D79&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J79" s="21" t="n"/>
@@ -3452,7 +3457,7 @@
         <v/>
       </c>
       <c r="I80" s="20">
-        <f>IF($D80="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D80="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D80)*($D80&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J80" s="21" t="n"/>
@@ -3475,7 +3480,7 @@
         <v/>
       </c>
       <c r="I81" s="20">
-        <f>IF($D81="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D81="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D81)*($D81&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J81" s="21" t="n"/>
@@ -3498,7 +3503,7 @@
         <v/>
       </c>
       <c r="I82" s="20">
-        <f>IF($D82="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D82="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D82)*($D82&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J82" s="21" t="n"/>
@@ -3521,7 +3526,7 @@
         <v/>
       </c>
       <c r="I83" s="20">
-        <f>IF($D83="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D83="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D83)*($D83&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J83" s="21" t="n"/>
@@ -3544,7 +3549,7 @@
         <v/>
       </c>
       <c r="I84" s="20">
-        <f>IF($D84="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D84="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D84)*($D84&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J84" s="21" t="n"/>
@@ -3567,7 +3572,7 @@
         <v/>
       </c>
       <c r="I85" s="20">
-        <f>IF($D85="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D85="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D85)*($D85&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J85" s="21" t="n"/>
@@ -3590,7 +3595,7 @@
         <v/>
       </c>
       <c r="I86" s="20">
-        <f>IF($D86="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D86="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D86)*($D86&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J86" s="21" t="n"/>
@@ -3613,7 +3618,7 @@
         <v/>
       </c>
       <c r="I87" s="20">
-        <f>IF($D87="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D87="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D87)*($D87&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J87" s="21" t="n"/>
@@ -3636,7 +3641,7 @@
         <v/>
       </c>
       <c r="I88" s="20">
-        <f>IF($D88="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D88="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D88)*($D88&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J88" s="21" t="n"/>
@@ -3659,7 +3664,7 @@
         <v/>
       </c>
       <c r="I89" s="20">
-        <f>IF($D89="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D89="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D89)*($D89&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J89" s="21" t="n"/>
@@ -3682,7 +3687,7 @@
         <v/>
       </c>
       <c r="I90" s="20">
-        <f>IF($D90="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D90="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D90)*($D90&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J90" s="21" t="n"/>
@@ -3705,7 +3710,7 @@
         <v/>
       </c>
       <c r="I91" s="20">
-        <f>IF($D91="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D91="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D91)*($D91&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J91" s="21" t="n"/>
@@ -3728,7 +3733,7 @@
         <v/>
       </c>
       <c r="I92" s="20">
-        <f>IF($D92="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D92="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D92)*($D92&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J92" s="21" t="n"/>
@@ -3751,7 +3756,7 @@
         <v/>
       </c>
       <c r="I93" s="20">
-        <f>IF($D93="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D93="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D93)*($D93&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J93" s="21" t="n"/>
@@ -3774,7 +3779,7 @@
         <v/>
       </c>
       <c r="I94" s="20">
-        <f>IF($D94="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D94="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D94)*($D94&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J94" s="21" t="n"/>
@@ -3797,7 +3802,7 @@
         <v/>
       </c>
       <c r="I95" s="20">
-        <f>IF($D95="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D95="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D95)*($D95&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J95" s="21" t="n"/>
@@ -3820,7 +3825,7 @@
         <v/>
       </c>
       <c r="I96" s="20">
-        <f>IF($D96="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D96="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D96)*($D96&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J96" s="21" t="n"/>
@@ -3843,7 +3848,7 @@
         <v/>
       </c>
       <c r="I97" s="20">
-        <f>IF($D97="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D97="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D97)*($D97&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J97" s="21" t="n"/>
@@ -3866,7 +3871,7 @@
         <v/>
       </c>
       <c r="I98" s="20">
-        <f>IF($D98="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D98="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D98)*($D98&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J98" s="21" t="n"/>
@@ -3889,7 +3894,7 @@
         <v/>
       </c>
       <c r="I99" s="20">
-        <f>IF($D99="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D99="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D99)*($D99&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J99" s="21" t="n"/>
@@ -3912,7 +3917,7 @@
         <v/>
       </c>
       <c r="I100" s="20">
-        <f>IF($D100="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D100="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D100)*($D100&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J100" s="21" t="n"/>
@@ -3935,7 +3940,7 @@
         <v/>
       </c>
       <c r="I101" s="20">
-        <f>IF($D101="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D101="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D101)*($D101&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J101" s="21" t="n"/>
@@ -3958,7 +3963,7 @@
         <v/>
       </c>
       <c r="I102" s="20">
-        <f>IF($D102="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D102="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D102)*($D102&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J102" s="21" t="n"/>
@@ -3981,7 +3986,7 @@
         <v/>
       </c>
       <c r="I103" s="20">
-        <f>IF($D103="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D103="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D103)*($D103&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J103" s="21" t="n"/>
@@ -4004,7 +4009,7 @@
         <v/>
       </c>
       <c r="I104" s="20">
-        <f>IF($D104="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;'الإعدادات والقوائم'!$B$6,"⚠ تجاوز الحد ("&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;")","✓ ضمن الحد"))</f>
+        <f>IF($D104="","",IF(SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))&gt;MaxLeave,"⚠ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave,"✓ مجازين "&amp;SUMPRODUCT(('حجز الإجازات'!$G$5:$G$104&lt;&gt;"مرفوض")*('حجز الإجازات'!$D$5:$D$104&lt;=$D104)*($D104&lt;=('حجز الإجازات'!$E$5:$E$104)))&amp;" / الحد "&amp;MaxLeave))</f>
         <v/>
       </c>
       <c r="J104" s="21" t="n"/>
@@ -4395,127 +4400,127 @@
         <v/>
       </c>
       <c r="D4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$2,"",IF(MOD(D$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$2,"",IF(MOD(D$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$2,"",IF(MOD(E$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$2,"",IF(MOD(E$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$2,"",IF(MOD(F$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$2,"",IF(MOD(F$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$2,"",IF(MOD(G$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$2,"",IF(MOD(G$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$2,"",IF(MOD(H$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$2,"",IF(MOD(H$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$2,"",IF(MOD(I$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$2,"",IF(MOD(I$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$2,"",IF(MOD(J$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$2,"",IF(MOD(J$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$2,"",IF(MOD(K$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$2,"",IF(MOD(K$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$2,"",IF(MOD(L$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$2,"",IF(MOD(L$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$2,"",IF(MOD(M$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$2,"",IF(MOD(M$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$2,"",IF(MOD(N$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$2,"",IF(MOD(N$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$2,"",IF(MOD(O$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$2,"",IF(MOD(O$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$2,"",IF(MOD(P$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$2,"",IF(MOD(P$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$2,"",IF(MOD(Q$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$2,"",IF(MOD(Q$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$2,"",IF(MOD(R$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$2,"",IF(MOD(R$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$2,"",IF(MOD(S$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$2,"",IF(MOD(S$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$2,"",IF(MOD(T$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$2,"",IF(MOD(T$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$2,"",IF(MOD(U$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$2,"",IF(MOD(U$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$2,"",IF(MOD(V$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$2,"",IF(MOD(V$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$2,"",IF(MOD(W$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$2,"",IF(MOD(W$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$2,"",IF(MOD(X$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$2,"",IF(MOD(X$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$2,"",IF(MOD(Y$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$2,"",IF(MOD(Y$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$2,"",IF(MOD(Z$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$2,"",IF(MOD(Z$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$2,"",IF(MOD(AA$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$2,"",IF(MOD(AA$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$2,"",IF(MOD(AB$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$2,"",IF(MOD(AB$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$2,"",IF(MOD(AC$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$2,"",IF(MOD(AC$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$2,"",IF(MOD(AD$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$2,"",IF(MOD(AD$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$2,"",IF(MOD(AE$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$2,"",IF(MOD(AE$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$2,"",IF(MOD(AF$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$2,"",IF(MOD(AF$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$2,"",IF(MOD(AG$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$2,"",IF(MOD(AG$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH4" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$2,"",IF(MOD(AH$3-'الموظفون'!$E$2,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$2,"",IF(MOD(AH$3-'الموظفون'!$E$2,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$2,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$2)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -4532,127 +4537,127 @@
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$3,"",IF(MOD(D$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$3,"",IF(MOD(D$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$3,"",IF(MOD(E$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$3,"",IF(MOD(E$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$3,"",IF(MOD(F$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$3,"",IF(MOD(F$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$3,"",IF(MOD(G$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$3,"",IF(MOD(G$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$3,"",IF(MOD(H$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$3,"",IF(MOD(H$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$3,"",IF(MOD(I$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$3,"",IF(MOD(I$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$3,"",IF(MOD(J$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$3,"",IF(MOD(J$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$3,"",IF(MOD(K$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$3,"",IF(MOD(K$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$3,"",IF(MOD(L$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$3,"",IF(MOD(L$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$3,"",IF(MOD(M$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$3,"",IF(MOD(M$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$3,"",IF(MOD(N$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$3,"",IF(MOD(N$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$3,"",IF(MOD(O$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$3,"",IF(MOD(O$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$3,"",IF(MOD(P$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$3,"",IF(MOD(P$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$3,"",IF(MOD(Q$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$3,"",IF(MOD(Q$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$3,"",IF(MOD(R$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$3,"",IF(MOD(R$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$3,"",IF(MOD(S$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$3,"",IF(MOD(S$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$3,"",IF(MOD(T$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$3,"",IF(MOD(T$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$3,"",IF(MOD(U$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$3,"",IF(MOD(U$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$3,"",IF(MOD(V$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$3,"",IF(MOD(V$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$3,"",IF(MOD(W$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$3,"",IF(MOD(W$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$3,"",IF(MOD(X$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$3,"",IF(MOD(X$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$3,"",IF(MOD(Y$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$3,"",IF(MOD(Y$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$3,"",IF(MOD(Z$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$3,"",IF(MOD(Z$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$3,"",IF(MOD(AA$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$3,"",IF(MOD(AA$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$3,"",IF(MOD(AB$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$3,"",IF(MOD(AB$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$3,"",IF(MOD(AC$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$3,"",IF(MOD(AC$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$3,"",IF(MOD(AD$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$3,"",IF(MOD(AD$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$3,"",IF(MOD(AE$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$3,"",IF(MOD(AE$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$3,"",IF(MOD(AF$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$3,"",IF(MOD(AF$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$3,"",IF(MOD(AG$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$3,"",IF(MOD(AG$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH5" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$3,"",IF(MOD(AH$3-'الموظفون'!$E$3,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$3,"",IF(MOD(AH$3-'الموظفون'!$E$3,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$3,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$3)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -4669,127 +4674,127 @@
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$4,"",IF(MOD(D$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$4,"",IF(MOD(D$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$4,"",IF(MOD(E$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$4,"",IF(MOD(E$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$4,"",IF(MOD(F$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$4,"",IF(MOD(F$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$4,"",IF(MOD(G$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$4,"",IF(MOD(G$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$4,"",IF(MOD(H$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$4,"",IF(MOD(H$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$4,"",IF(MOD(I$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$4,"",IF(MOD(I$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$4,"",IF(MOD(J$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$4,"",IF(MOD(J$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$4,"",IF(MOD(K$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$4,"",IF(MOD(K$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$4,"",IF(MOD(L$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$4,"",IF(MOD(L$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$4,"",IF(MOD(M$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$4,"",IF(MOD(M$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$4,"",IF(MOD(N$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$4,"",IF(MOD(N$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$4,"",IF(MOD(O$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$4,"",IF(MOD(O$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$4,"",IF(MOD(P$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$4,"",IF(MOD(P$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$4,"",IF(MOD(Q$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$4,"",IF(MOD(Q$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$4,"",IF(MOD(R$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$4,"",IF(MOD(R$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$4,"",IF(MOD(S$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$4,"",IF(MOD(S$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$4,"",IF(MOD(T$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$4,"",IF(MOD(T$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$4,"",IF(MOD(U$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$4,"",IF(MOD(U$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$4,"",IF(MOD(V$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$4,"",IF(MOD(V$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$4,"",IF(MOD(W$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$4,"",IF(MOD(W$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$4,"",IF(MOD(X$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$4,"",IF(MOD(X$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$4,"",IF(MOD(Y$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$4,"",IF(MOD(Y$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$4,"",IF(MOD(Z$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$4,"",IF(MOD(Z$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$4,"",IF(MOD(AA$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$4,"",IF(MOD(AA$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$4,"",IF(MOD(AB$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$4,"",IF(MOD(AB$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$4,"",IF(MOD(AC$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$4,"",IF(MOD(AC$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$4,"",IF(MOD(AD$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$4,"",IF(MOD(AD$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$4,"",IF(MOD(AE$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$4,"",IF(MOD(AE$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$4,"",IF(MOD(AF$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$4,"",IF(MOD(AF$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$4,"",IF(MOD(AG$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$4,"",IF(MOD(AG$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH6" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$4,"",IF(MOD(AH$3-'الموظفون'!$E$4,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$4,"",IF(MOD(AH$3-'الموظفون'!$E$4,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$4,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$4)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -4806,127 +4811,127 @@
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$5,"",IF(MOD(D$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$5,"",IF(MOD(D$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$5,"",IF(MOD(E$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$5,"",IF(MOD(E$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$5,"",IF(MOD(F$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$5,"",IF(MOD(F$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$5,"",IF(MOD(G$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$5,"",IF(MOD(G$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$5,"",IF(MOD(H$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$5,"",IF(MOD(H$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$5,"",IF(MOD(I$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$5,"",IF(MOD(I$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$5,"",IF(MOD(J$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$5,"",IF(MOD(J$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$5,"",IF(MOD(K$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$5,"",IF(MOD(K$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$5,"",IF(MOD(L$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$5,"",IF(MOD(L$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$5,"",IF(MOD(M$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$5,"",IF(MOD(M$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$5,"",IF(MOD(N$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$5,"",IF(MOD(N$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$5,"",IF(MOD(O$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$5,"",IF(MOD(O$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$5,"",IF(MOD(P$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$5,"",IF(MOD(P$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$5,"",IF(MOD(Q$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$5,"",IF(MOD(Q$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$5,"",IF(MOD(R$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$5,"",IF(MOD(R$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$5,"",IF(MOD(S$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$5,"",IF(MOD(S$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$5,"",IF(MOD(T$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$5,"",IF(MOD(T$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$5,"",IF(MOD(U$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$5,"",IF(MOD(U$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$5,"",IF(MOD(V$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$5,"",IF(MOD(V$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$5,"",IF(MOD(W$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$5,"",IF(MOD(W$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$5,"",IF(MOD(X$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$5,"",IF(MOD(X$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$5,"",IF(MOD(Y$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$5,"",IF(MOD(Y$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$5,"",IF(MOD(Z$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$5,"",IF(MOD(Z$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$5,"",IF(MOD(AA$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$5,"",IF(MOD(AA$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$5,"",IF(MOD(AB$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$5,"",IF(MOD(AB$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$5,"",IF(MOD(AC$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$5,"",IF(MOD(AC$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$5,"",IF(MOD(AD$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$5,"",IF(MOD(AD$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$5,"",IF(MOD(AE$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$5,"",IF(MOD(AE$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$5,"",IF(MOD(AF$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$5,"",IF(MOD(AF$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$5,"",IF(MOD(AG$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$5,"",IF(MOD(AG$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH7" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$5,"",IF(MOD(AH$3-'الموظفون'!$E$5,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$5,"",IF(MOD(AH$3-'الموظفون'!$E$5,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$5,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$5)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -4943,127 +4948,127 @@
         <v/>
       </c>
       <c r="D8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$6,"",IF(MOD(D$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$6,"",IF(MOD(D$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$6,"",IF(MOD(E$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$6,"",IF(MOD(E$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$6,"",IF(MOD(F$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$6,"",IF(MOD(F$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$6,"",IF(MOD(G$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$6,"",IF(MOD(G$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$6,"",IF(MOD(H$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$6,"",IF(MOD(H$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$6,"",IF(MOD(I$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$6,"",IF(MOD(I$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$6,"",IF(MOD(J$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$6,"",IF(MOD(J$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$6,"",IF(MOD(K$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$6,"",IF(MOD(K$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$6,"",IF(MOD(L$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$6,"",IF(MOD(L$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$6,"",IF(MOD(M$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$6,"",IF(MOD(M$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$6,"",IF(MOD(N$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$6,"",IF(MOD(N$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$6,"",IF(MOD(O$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$6,"",IF(MOD(O$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$6,"",IF(MOD(P$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$6,"",IF(MOD(P$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$6,"",IF(MOD(Q$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$6,"",IF(MOD(Q$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$6,"",IF(MOD(R$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$6,"",IF(MOD(R$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$6,"",IF(MOD(S$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$6,"",IF(MOD(S$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$6,"",IF(MOD(T$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$6,"",IF(MOD(T$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$6,"",IF(MOD(U$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$6,"",IF(MOD(U$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$6,"",IF(MOD(V$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$6,"",IF(MOD(V$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$6,"",IF(MOD(W$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$6,"",IF(MOD(W$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$6,"",IF(MOD(X$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$6,"",IF(MOD(X$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$6,"",IF(MOD(Y$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$6,"",IF(MOD(Y$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$6,"",IF(MOD(Z$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$6,"",IF(MOD(Z$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$6,"",IF(MOD(AA$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$6,"",IF(MOD(AA$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$6,"",IF(MOD(AB$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$6,"",IF(MOD(AB$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$6,"",IF(MOD(AC$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$6,"",IF(MOD(AC$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$6,"",IF(MOD(AD$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$6,"",IF(MOD(AD$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$6,"",IF(MOD(AE$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$6,"",IF(MOD(AE$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$6,"",IF(MOD(AF$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$6,"",IF(MOD(AF$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$6,"",IF(MOD(AG$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$6,"",IF(MOD(AG$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH8" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$6,"",IF(MOD(AH$3-'الموظفون'!$E$6,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$6,"",IF(MOD(AH$3-'الموظفون'!$E$6,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$6,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$6)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -5080,127 +5085,127 @@
         <v/>
       </c>
       <c r="D9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$7,"",IF(MOD(D$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$7,"",IF(MOD(D$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$7,"",IF(MOD(E$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$7,"",IF(MOD(E$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$7,"",IF(MOD(F$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$7,"",IF(MOD(F$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$7,"",IF(MOD(G$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$7,"",IF(MOD(G$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$7,"",IF(MOD(H$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$7,"",IF(MOD(H$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$7,"",IF(MOD(I$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$7,"",IF(MOD(I$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$7,"",IF(MOD(J$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$7,"",IF(MOD(J$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$7,"",IF(MOD(K$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$7,"",IF(MOD(K$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$7,"",IF(MOD(L$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$7,"",IF(MOD(L$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$7,"",IF(MOD(M$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$7,"",IF(MOD(M$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$7,"",IF(MOD(N$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$7,"",IF(MOD(N$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$7,"",IF(MOD(O$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$7,"",IF(MOD(O$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$7,"",IF(MOD(P$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$7,"",IF(MOD(P$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$7,"",IF(MOD(Q$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$7,"",IF(MOD(Q$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$7,"",IF(MOD(R$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$7,"",IF(MOD(R$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$7,"",IF(MOD(S$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$7,"",IF(MOD(S$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$7,"",IF(MOD(T$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$7,"",IF(MOD(T$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$7,"",IF(MOD(U$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$7,"",IF(MOD(U$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$7,"",IF(MOD(V$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$7,"",IF(MOD(V$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$7,"",IF(MOD(W$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$7,"",IF(MOD(W$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$7,"",IF(MOD(X$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$7,"",IF(MOD(X$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$7,"",IF(MOD(Y$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$7,"",IF(MOD(Y$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$7,"",IF(MOD(Z$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$7,"",IF(MOD(Z$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$7,"",IF(MOD(AA$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$7,"",IF(MOD(AA$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$7,"",IF(MOD(AB$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$7,"",IF(MOD(AB$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$7,"",IF(MOD(AC$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$7,"",IF(MOD(AC$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$7,"",IF(MOD(AD$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$7,"",IF(MOD(AD$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$7,"",IF(MOD(AE$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$7,"",IF(MOD(AE$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$7,"",IF(MOD(AF$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$7,"",IF(MOD(AF$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$7,"",IF(MOD(AG$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$7,"",IF(MOD(AG$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH9" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$7,"",IF(MOD(AH$3-'الموظفون'!$E$7,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$7,"",IF(MOD(AH$3-'الموظفون'!$E$7,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$7,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$7)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -5217,127 +5222,127 @@
         <v/>
       </c>
       <c r="D10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$8,"",IF(MOD(D$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$8,"",IF(MOD(D$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$8,"",IF(MOD(E$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$8,"",IF(MOD(E$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$8,"",IF(MOD(F$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$8,"",IF(MOD(F$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$8,"",IF(MOD(G$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$8,"",IF(MOD(G$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$8,"",IF(MOD(H$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$8,"",IF(MOD(H$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$8,"",IF(MOD(I$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$8,"",IF(MOD(I$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$8,"",IF(MOD(J$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$8,"",IF(MOD(J$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$8,"",IF(MOD(K$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$8,"",IF(MOD(K$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$8,"",IF(MOD(L$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$8,"",IF(MOD(L$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$8,"",IF(MOD(M$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$8,"",IF(MOD(M$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$8,"",IF(MOD(N$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$8,"",IF(MOD(N$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$8,"",IF(MOD(O$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$8,"",IF(MOD(O$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$8,"",IF(MOD(P$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$8,"",IF(MOD(P$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$8,"",IF(MOD(Q$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$8,"",IF(MOD(Q$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$8,"",IF(MOD(R$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$8,"",IF(MOD(R$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$8,"",IF(MOD(S$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$8,"",IF(MOD(S$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$8,"",IF(MOD(T$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$8,"",IF(MOD(T$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$8,"",IF(MOD(U$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$8,"",IF(MOD(U$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$8,"",IF(MOD(V$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$8,"",IF(MOD(V$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$8,"",IF(MOD(W$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$8,"",IF(MOD(W$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$8,"",IF(MOD(X$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$8,"",IF(MOD(X$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$8,"",IF(MOD(Y$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$8,"",IF(MOD(Y$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$8,"",IF(MOD(Z$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$8,"",IF(MOD(Z$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$8,"",IF(MOD(AA$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$8,"",IF(MOD(AA$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$8,"",IF(MOD(AB$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$8,"",IF(MOD(AB$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$8,"",IF(MOD(AC$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$8,"",IF(MOD(AC$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$8,"",IF(MOD(AD$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$8,"",IF(MOD(AD$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$8,"",IF(MOD(AE$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$8,"",IF(MOD(AE$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$8,"",IF(MOD(AF$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$8,"",IF(MOD(AF$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$8,"",IF(MOD(AG$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$8,"",IF(MOD(AG$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH10" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$8,"",IF(MOD(AH$3-'الموظفون'!$E$8,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$8,"",IF(MOD(AH$3-'الموظفون'!$E$8,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$8,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$8)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -5354,127 +5359,127 @@
         <v/>
       </c>
       <c r="D11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$9,"",IF(MOD(D$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(D$3&lt;'الموظفون'!$E$9,"",IF(MOD(D$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=D$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=D$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$9,"",IF(MOD(E$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(E$3&lt;'الموظفون'!$E$9,"",IF(MOD(E$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=E$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=E$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="F11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$9,"",IF(MOD(F$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(F$3&lt;'الموظفون'!$E$9,"",IF(MOD(F$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=F$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=F$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$9,"",IF(MOD(G$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(G$3&lt;'الموظفون'!$E$9,"",IF(MOD(G$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=G$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=G$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="H11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$9,"",IF(MOD(H$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(H$3&lt;'الموظفون'!$E$9,"",IF(MOD(H$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=H$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=H$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="I11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$9,"",IF(MOD(I$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(I$3&lt;'الموظفون'!$E$9,"",IF(MOD(I$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=I$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=I$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="J11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$9,"",IF(MOD(J$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(J$3&lt;'الموظفون'!$E$9,"",IF(MOD(J$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=J$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=J$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="K11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$9,"",IF(MOD(K$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(K$3&lt;'الموظفون'!$E$9,"",IF(MOD(K$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=K$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=K$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="L11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$9,"",IF(MOD(L$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(L$3&lt;'الموظفون'!$E$9,"",IF(MOD(L$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=L$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=L$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="M11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$9,"",IF(MOD(M$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(M$3&lt;'الموظفون'!$E$9,"",IF(MOD(M$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=M$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=M$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="N11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$9,"",IF(MOD(N$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(N$3&lt;'الموظفون'!$E$9,"",IF(MOD(N$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=N$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=N$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="O11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$9,"",IF(MOD(O$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(O$3&lt;'الموظفون'!$E$9,"",IF(MOD(O$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=O$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=O$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="P11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$9,"",IF(MOD(P$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(P$3&lt;'الموظفون'!$E$9,"",IF(MOD(P$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=P$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=P$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Q11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$9,"",IF(MOD(Q$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Q$3&lt;'الموظفون'!$E$9,"",IF(MOD(Q$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Q$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Q$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="R11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$9,"",IF(MOD(R$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(R$3&lt;'الموظفون'!$E$9,"",IF(MOD(R$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=R$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=R$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="S11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$9,"",IF(MOD(S$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(S$3&lt;'الموظفون'!$E$9,"",IF(MOD(S$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=S$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=S$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="T11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$9,"",IF(MOD(T$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(T$3&lt;'الموظفون'!$E$9,"",IF(MOD(T$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=T$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=T$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="U11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$9,"",IF(MOD(U$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(U$3&lt;'الموظفون'!$E$9,"",IF(MOD(U$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=U$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=U$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="V11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$9,"",IF(MOD(V$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(V$3&lt;'الموظفون'!$E$9,"",IF(MOD(V$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=V$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=V$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="W11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$9,"",IF(MOD(W$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(W$3&lt;'الموظفون'!$E$9,"",IF(MOD(W$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=W$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=W$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="X11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$9,"",IF(MOD(X$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(X$3&lt;'الموظفون'!$E$9,"",IF(MOD(X$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=X$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=X$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Y11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$9,"",IF(MOD(Y$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Y$3&lt;'الموظفون'!$E$9,"",IF(MOD(Y$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Y$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Y$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="Z11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$9,"",IF(MOD(Z$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(Z$3&lt;'الموظفون'!$E$9,"",IF(MOD(Z$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=Z$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=Z$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AA11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$9,"",IF(MOD(AA$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AA$3&lt;'الموظفون'!$E$9,"",IF(MOD(AA$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AA$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AA$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AB11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$9,"",IF(MOD(AB$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AB$3&lt;'الموظفون'!$E$9,"",IF(MOD(AB$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AB$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AB$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AC11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$9,"",IF(MOD(AC$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AC$3&lt;'الموظفون'!$E$9,"",IF(MOD(AC$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AC$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AC$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AD11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$9,"",IF(MOD(AD$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AD$3&lt;'الموظفون'!$E$9,"",IF(MOD(AD$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AD$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AD$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AE11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$9,"",IF(MOD(AE$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AE$3&lt;'الموظفون'!$E$9,"",IF(MOD(AE$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AE$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AE$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AF11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$9,"",IF(MOD(AF$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AF$3&lt;'الموظفون'!$E$9,"",IF(MOD(AF$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AF$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AF$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AG11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$9,"",IF(MOD(AG$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AG$3&lt;'الموظفون'!$E$9,"",IF(MOD(AG$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AG$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AG$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
       <c r="AH11" s="30">
-        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$9,"",IF(MOD(AH$3-'الموظفون'!$E$9,'الإعدادات والقوائم'!$B$3+'الإعدادات والقوائم'!$B$4)&lt;'الإعدادات والقوائم'!$B$3,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
+        <f>IF(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104))=0,IF(AH$3&lt;'الموظفون'!$E$9,"",IF(MOD(AH$3-'الموظفون'!$E$9,CycleWork+CycleRest)&lt;CycleWork,'الموظفون'!$D$9,"راحة")),INDEX('حجز الإجازات'!$C$5:$C$104,(SUMPRODUCT(('حجز الإجازات'!$B$5:$B$104='الموظفون'!$B$9)*('حجز الإجازات'!$D$5:$D$104&lt;=AH$3)*(('حجز الإجازات'!$E$5:$E$104)&gt;=AH$3)*('حجز الإجازات'!$G$5:$G$104="معتمد")*ROW('حجز الإجازات'!$B$5:$B$104)))-5+1))</f>
         <v/>
       </c>
     </row>
@@ -6213,157 +6218,157 @@
   </sheetData>
   <conditionalFormatting sqref="D15">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15">
     <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
     <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
     <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
     <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
     <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
     <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N15">
     <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O15">
     <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P15">
     <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15">
     <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R15">
     <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S15">
     <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T15">
     <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U15">
     <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V15">
     <cfRule type="cellIs" priority="19" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W15">
     <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X15">
     <cfRule type="cellIs" priority="21" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y15">
     <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z15">
     <cfRule type="cellIs" priority="23" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA15">
     <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB15">
     <cfRule type="cellIs" priority="25" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC15">
     <cfRule type="cellIs" priority="26" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD15">
     <cfRule type="cellIs" priority="27" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE15">
     <cfRule type="cellIs" priority="28" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF15">
     <cfRule type="cellIs" priority="29" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG15">
     <cfRule type="cellIs" priority="30" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH15">
     <cfRule type="cellIs" priority="31" operator="lessThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$5</formula>
+      <formula>MinStaff</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:AH11">
@@ -8043,157 +8048,157 @@
   </sheetData>
   <conditionalFormatting sqref="D12">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12">
     <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
     <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
     <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
     <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L12">
     <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12">
     <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
     <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O12">
     <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12">
     <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
     <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
     <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12">
     <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12">
     <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U12">
     <cfRule type="cellIs" priority="18" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12">
     <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W12">
     <cfRule type="cellIs" priority="20" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X12">
     <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12">
     <cfRule type="cellIs" priority="22" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z12">
     <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA12">
     <cfRule type="cellIs" priority="24" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB12">
     <cfRule type="cellIs" priority="25" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC12">
     <cfRule type="cellIs" priority="26" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD12">
     <cfRule type="cellIs" priority="27" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE12">
     <cfRule type="cellIs" priority="28" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF12">
     <cfRule type="cellIs" priority="29" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG12">
     <cfRule type="cellIs" priority="30" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH12">
     <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="3">
-      <formula>'الإعدادات والقوائم'!$B$6</formula>
+      <formula>MaxLeave</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:AH11">
